--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C530"/>
+  <dimension ref="A1:C571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.000563</v>
+        <v>0.000497</v>
       </c>
       <c r="C287" t="n">
         <v>1</v>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.00074</v>
+        <v>0.000508</v>
       </c>
       <c r="C288" t="n">
-        <v>0.995902</v>
+        <v>0.996491</v>
       </c>
     </row>
     <row r="289">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.00132</v>
+        <v>0.001733</v>
       </c>
       <c r="C289" t="n">
-        <v>0.991803</v>
+        <v>0.992982</v>
       </c>
     </row>
     <row r="290">
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.001378</v>
+        <v>0.001931</v>
       </c>
       <c r="C290" t="n">
-        <v>0.9877050000000001</v>
+        <v>0.989474</v>
       </c>
     </row>
     <row r="291">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.001387</v>
+        <v>0.002521</v>
       </c>
       <c r="C291" t="n">
-        <v>0.983607</v>
+        <v>0.985965</v>
       </c>
     </row>
     <row r="292">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.001492</v>
+        <v>0.00258</v>
       </c>
       <c r="C292" t="n">
-        <v>0.979508</v>
+        <v>0.982456</v>
       </c>
     </row>
     <row r="293">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.001503</v>
+        <v>0.002867</v>
       </c>
       <c r="C293" t="n">
-        <v>0.97541</v>
+        <v>0.978947</v>
       </c>
     </row>
     <row r="294">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.001566</v>
+        <v>0.003785</v>
       </c>
       <c r="C294" t="n">
-        <v>0.971311</v>
+        <v>0.9754389999999999</v>
       </c>
     </row>
     <row r="295">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.002038</v>
+        <v>0.00387</v>
       </c>
       <c r="C295" t="n">
-        <v>0.967213</v>
+        <v>0.97193</v>
       </c>
     </row>
     <row r="296">
@@ -4262,10 +4262,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.002044</v>
+        <v>0.004113</v>
       </c>
       <c r="C296" t="n">
-        <v>0.9631150000000001</v>
+        <v>0.968421</v>
       </c>
     </row>
     <row r="297">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.00206</v>
+        <v>0.004158</v>
       </c>
       <c r="C297" t="n">
-        <v>0.959016</v>
+        <v>0.964912</v>
       </c>
     </row>
     <row r="298">
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.002131</v>
+        <v>0.004324</v>
       </c>
       <c r="C298" t="n">
-        <v>0.954918</v>
+        <v>0.961404</v>
       </c>
     </row>
     <row r="299">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.002193</v>
+        <v>0.004384</v>
       </c>
       <c r="C299" t="n">
-        <v>0.95082</v>
+        <v>0.9578950000000001</v>
       </c>
     </row>
     <row r="300">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.002225</v>
+        <v>0.004719</v>
       </c>
       <c r="C300" t="n">
-        <v>0.946721</v>
+        <v>0.954386</v>
       </c>
     </row>
     <row r="301">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.002351</v>
+        <v>0.00494</v>
       </c>
       <c r="C301" t="n">
-        <v>0.942623</v>
+        <v>0.950877</v>
       </c>
     </row>
     <row r="302">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.002614</v>
+        <v>0.005039</v>
       </c>
       <c r="C302" t="n">
-        <v>0.9385250000000001</v>
+        <v>0.947368</v>
       </c>
     </row>
     <row r="303">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.002915</v>
+        <v>0.005251</v>
       </c>
       <c r="C303" t="n">
-        <v>0.934426</v>
+        <v>0.94386</v>
       </c>
     </row>
     <row r="304">
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0.003143</v>
+        <v>0.005333</v>
       </c>
       <c r="C304" t="n">
-        <v>0.930328</v>
+        <v>0.940351</v>
       </c>
     </row>
     <row r="305">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.003726</v>
+        <v>0.005371</v>
       </c>
       <c r="C305" t="n">
-        <v>0.92623</v>
+        <v>0.936842</v>
       </c>
     </row>
     <row r="306">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.003827</v>
+        <v>0.005447</v>
       </c>
       <c r="C306" t="n">
-        <v>0.922131</v>
+        <v>0.933333</v>
       </c>
     </row>
     <row r="307">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>0.004072</v>
+        <v>0.005777</v>
       </c>
       <c r="C307" t="n">
-        <v>0.918033</v>
+        <v>0.929825</v>
       </c>
     </row>
     <row r="308">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0.004112</v>
+        <v>0.005837</v>
       </c>
       <c r="C308" t="n">
-        <v>0.913934</v>
+        <v>0.926316</v>
       </c>
     </row>
     <row r="309">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.004443</v>
+        <v>0.006082</v>
       </c>
       <c r="C309" t="n">
-        <v>0.909836</v>
+        <v>0.922807</v>
       </c>
     </row>
     <row r="310">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.004633</v>
+        <v>0.007774</v>
       </c>
       <c r="C310" t="n">
-        <v>0.905738</v>
+        <v>0.9192979999999999</v>
       </c>
     </row>
     <row r="311">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.004855</v>
+        <v>0.008286999999999999</v>
       </c>
       <c r="C311" t="n">
-        <v>0.901639</v>
+        <v>0.915789</v>
       </c>
     </row>
     <row r="312">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.004953</v>
+        <v>0.008463</v>
       </c>
       <c r="C312" t="n">
-        <v>0.897541</v>
+        <v>0.912281</v>
       </c>
     </row>
     <row r="313">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0.004955</v>
+        <v>0.008534999999999999</v>
       </c>
       <c r="C313" t="n">
-        <v>0.893443</v>
+        <v>0.908772</v>
       </c>
     </row>
     <row r="314">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.005172</v>
+        <v>0.009383000000000001</v>
       </c>
       <c r="C314" t="n">
-        <v>0.889344</v>
+        <v>0.905263</v>
       </c>
     </row>
     <row r="315">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.005365</v>
+        <v>0.009622</v>
       </c>
       <c r="C315" t="n">
-        <v>0.885246</v>
+        <v>0.9017539999999999</v>
       </c>
     </row>
     <row r="316">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.005832</v>
+        <v>0.009691</v>
       </c>
       <c r="C316" t="n">
-        <v>0.881148</v>
+        <v>0.898246</v>
       </c>
     </row>
     <row r="317">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.00596</v>
+        <v>0.009783999999999999</v>
       </c>
       <c r="C317" t="n">
-        <v>0.877049</v>
+        <v>0.894737</v>
       </c>
     </row>
     <row r="318">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.006011</v>
+        <v>0.009868999999999999</v>
       </c>
       <c r="C318" t="n">
-        <v>0.872951</v>
+        <v>0.891228</v>
       </c>
     </row>
     <row r="319">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.00611</v>
+        <v>0.010202</v>
       </c>
       <c r="C319" t="n">
-        <v>0.868852</v>
+        <v>0.887719</v>
       </c>
     </row>
     <row r="320">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.006439</v>
+        <v>0.010573</v>
       </c>
       <c r="C320" t="n">
-        <v>0.864754</v>
+        <v>0.884211</v>
       </c>
     </row>
     <row r="321">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.00653</v>
+        <v>0.010685</v>
       </c>
       <c r="C321" t="n">
-        <v>0.860656</v>
+        <v>0.880702</v>
       </c>
     </row>
     <row r="322">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.006564</v>
+        <v>0.010857</v>
       </c>
       <c r="C322" t="n">
-        <v>0.856557</v>
+        <v>0.877193</v>
       </c>
     </row>
     <row r="323">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.006747</v>
+        <v>0.010952</v>
       </c>
       <c r="C323" t="n">
-        <v>0.852459</v>
+        <v>0.873684</v>
       </c>
     </row>
     <row r="324">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.006802</v>
+        <v>0.010964</v>
       </c>
       <c r="C324" t="n">
-        <v>0.848361</v>
+        <v>0.870175</v>
       </c>
     </row>
     <row r="325">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.00685</v>
+        <v>0.011149</v>
       </c>
       <c r="C325" t="n">
-        <v>0.844262</v>
+        <v>0.866667</v>
       </c>
     </row>
     <row r="326">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.007166</v>
+        <v>0.011332</v>
       </c>
       <c r="C326" t="n">
-        <v>0.840164</v>
+        <v>0.863158</v>
       </c>
     </row>
     <row r="327">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.007171</v>
+        <v>0.012351</v>
       </c>
       <c r="C327" t="n">
-        <v>0.836066</v>
+        <v>0.859649</v>
       </c>
     </row>
     <row r="328">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.007299</v>
+        <v>0.012473</v>
       </c>
       <c r="C328" t="n">
-        <v>0.831967</v>
+        <v>0.85614</v>
       </c>
     </row>
     <row r="329">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.007556</v>
+        <v>0.013219</v>
       </c>
       <c r="C329" t="n">
-        <v>0.827869</v>
+        <v>0.8526319999999999</v>
       </c>
     </row>
     <row r="330">
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.007819</v>
+        <v>0.013467</v>
       </c>
       <c r="C330" t="n">
-        <v>0.82377</v>
+        <v>0.849123</v>
       </c>
     </row>
     <row r="331">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.007959000000000001</v>
+        <v>0.013541</v>
       </c>
       <c r="C331" t="n">
-        <v>0.819672</v>
+        <v>0.845614</v>
       </c>
     </row>
     <row r="332">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.007997000000000001</v>
+        <v>0.013546</v>
       </c>
       <c r="C332" t="n">
-        <v>0.815574</v>
+        <v>0.842105</v>
       </c>
     </row>
     <row r="333">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.008192</v>
+        <v>0.014397</v>
       </c>
       <c r="C333" t="n">
-        <v>0.8114749999999999</v>
+        <v>0.838596</v>
       </c>
     </row>
     <row r="334">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.008548999999999999</v>
+        <v>0.014864</v>
       </c>
       <c r="C334" t="n">
-        <v>0.807377</v>
+        <v>0.8350880000000001</v>
       </c>
     </row>
     <row r="335">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.008874999999999999</v>
+        <v>0.014868</v>
       </c>
       <c r="C335" t="n">
-        <v>0.803279</v>
+        <v>0.831579</v>
       </c>
     </row>
     <row r="336">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.008976</v>
+        <v>0.015452</v>
       </c>
       <c r="C336" t="n">
-        <v>0.79918</v>
+        <v>0.82807</v>
       </c>
     </row>
     <row r="337">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.009086</v>
+        <v>0.015572</v>
       </c>
       <c r="C337" t="n">
-        <v>0.795082</v>
+        <v>0.824561</v>
       </c>
     </row>
     <row r="338">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.009136999999999999</v>
+        <v>0.016035</v>
       </c>
       <c r="C338" t="n">
-        <v>0.790984</v>
+        <v>0.821053</v>
       </c>
     </row>
     <row r="339">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.009211</v>
+        <v>0.016162</v>
       </c>
       <c r="C339" t="n">
-        <v>0.7868849999999999</v>
+        <v>0.817544</v>
       </c>
     </row>
     <row r="340">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.009238</v>
+        <v>0.016231</v>
       </c>
       <c r="C340" t="n">
-        <v>0.782787</v>
+        <v>0.814035</v>
       </c>
     </row>
     <row r="341">
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.009424</v>
+        <v>0.016517</v>
       </c>
       <c r="C341" t="n">
-        <v>0.778689</v>
+        <v>0.810526</v>
       </c>
     </row>
     <row r="342">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.009466</v>
+        <v>0.017065</v>
       </c>
       <c r="C342" t="n">
-        <v>0.77459</v>
+        <v>0.807018</v>
       </c>
     </row>
     <row r="343">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.00966</v>
+        <v>0.017254</v>
       </c>
       <c r="C343" t="n">
-        <v>0.770492</v>
+        <v>0.803509</v>
       </c>
     </row>
     <row r="344">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.009990000000000001</v>
+        <v>0.017366</v>
       </c>
       <c r="C344" t="n">
-        <v>0.766393</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="345">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.010309</v>
+        <v>0.017998</v>
       </c>
       <c r="C345" t="n">
-        <v>0.7622949999999999</v>
+        <v>0.7964909999999999</v>
       </c>
     </row>
     <row r="346">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.010396</v>
+        <v>0.018188</v>
       </c>
       <c r="C346" t="n">
-        <v>0.758197</v>
+        <v>0.792982</v>
       </c>
     </row>
     <row r="347">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.010451</v>
+        <v>0.018379</v>
       </c>
       <c r="C347" t="n">
-        <v>0.754098</v>
+        <v>0.789474</v>
       </c>
     </row>
     <row r="348">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.010507</v>
+        <v>0.018767</v>
       </c>
       <c r="C348" t="n">
-        <v>0.75</v>
+        <v>0.785965</v>
       </c>
     </row>
     <row r="349">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.010536</v>
+        <v>0.018834</v>
       </c>
       <c r="C349" t="n">
-        <v>0.745902</v>
+        <v>0.782456</v>
       </c>
     </row>
     <row r="350">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.010864</v>
+        <v>0.019534</v>
       </c>
       <c r="C350" t="n">
-        <v>0.741803</v>
+        <v>0.7789469999999999</v>
       </c>
     </row>
     <row r="351">
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.01101</v>
+        <v>0.019751</v>
       </c>
       <c r="C351" t="n">
-        <v>0.7377050000000001</v>
+        <v>0.775439</v>
       </c>
     </row>
     <row r="352">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.011175</v>
+        <v>0.01998</v>
       </c>
       <c r="C352" t="n">
-        <v>0.733607</v>
+        <v>0.77193</v>
       </c>
     </row>
     <row r="353">
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.01137</v>
+        <v>0.020583</v>
       </c>
       <c r="C353" t="n">
-        <v>0.729508</v>
+        <v>0.768421</v>
       </c>
     </row>
     <row r="354">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.011371</v>
+        <v>0.021065</v>
       </c>
       <c r="C354" t="n">
-        <v>0.72541</v>
+        <v>0.764912</v>
       </c>
     </row>
     <row r="355">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.011389</v>
+        <v>0.021329</v>
       </c>
       <c r="C355" t="n">
-        <v>0.721311</v>
+        <v>0.761404</v>
       </c>
     </row>
     <row r="356">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.01146</v>
+        <v>0.02154</v>
       </c>
       <c r="C356" t="n">
-        <v>0.717213</v>
+        <v>0.757895</v>
       </c>
     </row>
     <row r="357">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.011806</v>
+        <v>0.021805</v>
       </c>
       <c r="C357" t="n">
-        <v>0.7131150000000001</v>
+        <v>0.754386</v>
       </c>
     </row>
     <row r="358">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.011893</v>
+        <v>0.02251</v>
       </c>
       <c r="C358" t="n">
-        <v>0.709016</v>
+        <v>0.750877</v>
       </c>
     </row>
     <row r="359">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.012101</v>
+        <v>0.02277</v>
       </c>
       <c r="C359" t="n">
-        <v>0.704918</v>
+        <v>0.747368</v>
       </c>
     </row>
     <row r="360">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.012352</v>
+        <v>0.023713</v>
       </c>
       <c r="C360" t="n">
-        <v>0.70082</v>
+        <v>0.74386</v>
       </c>
     </row>
     <row r="361">
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.012418</v>
+        <v>0.024241</v>
       </c>
       <c r="C361" t="n">
-        <v>0.696721</v>
+        <v>0.740351</v>
       </c>
     </row>
     <row r="362">
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.012538</v>
+        <v>0.02433</v>
       </c>
       <c r="C362" t="n">
-        <v>0.692623</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="363">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.012704</v>
+        <v>0.024547</v>
       </c>
       <c r="C363" t="n">
-        <v>0.6885250000000001</v>
+        <v>0.733333</v>
       </c>
     </row>
     <row r="364">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.012866</v>
+        <v>0.024699</v>
       </c>
       <c r="C364" t="n">
-        <v>0.684426</v>
+        <v>0.7298249999999999</v>
       </c>
     </row>
     <row r="365">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.012973</v>
+        <v>0.024807</v>
       </c>
       <c r="C365" t="n">
-        <v>0.680328</v>
+        <v>0.726316</v>
       </c>
     </row>
     <row r="366">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.013345</v>
+        <v>0.024984</v>
       </c>
       <c r="C366" t="n">
-        <v>0.67623</v>
+        <v>0.722807</v>
       </c>
     </row>
     <row r="367">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.013428</v>
+        <v>0.02537</v>
       </c>
       <c r="C367" t="n">
-        <v>0.672131</v>
+        <v>0.719298</v>
       </c>
     </row>
     <row r="368">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.014094</v>
+        <v>0.027088</v>
       </c>
       <c r="C368" t="n">
-        <v>0.668033</v>
+        <v>0.715789</v>
       </c>
     </row>
     <row r="369">
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.014264</v>
+        <v>0.027482</v>
       </c>
       <c r="C369" t="n">
-        <v>0.663934</v>
+        <v>0.7122810000000001</v>
       </c>
     </row>
     <row r="370">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.014338</v>
+        <v>0.027655</v>
       </c>
       <c r="C370" t="n">
-        <v>0.659836</v>
+        <v>0.708772</v>
       </c>
     </row>
     <row r="371">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.014424</v>
+        <v>0.028192</v>
       </c>
       <c r="C371" t="n">
-        <v>0.655738</v>
+        <v>0.705263</v>
       </c>
     </row>
     <row r="372">
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.014441</v>
+        <v>0.028362</v>
       </c>
       <c r="C372" t="n">
-        <v>0.651639</v>
+        <v>0.701754</v>
       </c>
     </row>
     <row r="373">
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.014536</v>
+        <v>0.028467</v>
       </c>
       <c r="C373" t="n">
-        <v>0.647541</v>
+        <v>0.698246</v>
       </c>
     </row>
     <row r="374">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.014714</v>
+        <v>0.028515</v>
       </c>
       <c r="C374" t="n">
-        <v>0.643443</v>
+        <v>0.694737</v>
       </c>
     </row>
     <row r="375">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.014849</v>
+        <v>0.028936</v>
       </c>
       <c r="C375" t="n">
-        <v>0.639344</v>
+        <v>0.691228</v>
       </c>
     </row>
     <row r="376">
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.014916</v>
+        <v>0.029992</v>
       </c>
       <c r="C376" t="n">
-        <v>0.635246</v>
+        <v>0.687719</v>
       </c>
     </row>
     <row r="377">
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.015887</v>
+        <v>0.030083</v>
       </c>
       <c r="C377" t="n">
-        <v>0.631148</v>
+        <v>0.684211</v>
       </c>
     </row>
     <row r="378">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.016892</v>
+        <v>0.030551</v>
       </c>
       <c r="C378" t="n">
-        <v>0.627049</v>
+        <v>0.680702</v>
       </c>
     </row>
     <row r="379">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.017236</v>
+        <v>0.0308</v>
       </c>
       <c r="C379" t="n">
-        <v>0.622951</v>
+        <v>0.677193</v>
       </c>
     </row>
     <row r="380">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.017289</v>
+        <v>0.03157</v>
       </c>
       <c r="C380" t="n">
-        <v>0.618852</v>
+        <v>0.6736839999999999</v>
       </c>
     </row>
     <row r="381">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.017313</v>
+        <v>0.031584</v>
       </c>
       <c r="C381" t="n">
-        <v>0.614754</v>
+        <v>0.670175</v>
       </c>
     </row>
     <row r="382">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.017531</v>
+        <v>0.031752</v>
       </c>
       <c r="C382" t="n">
-        <v>0.610656</v>
+        <v>0.666667</v>
       </c>
     </row>
     <row r="383">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.018129</v>
+        <v>0.031813</v>
       </c>
       <c r="C383" t="n">
-        <v>0.606557</v>
+        <v>0.663158</v>
       </c>
     </row>
     <row r="384">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.018178</v>
+        <v>0.031993</v>
       </c>
       <c r="C384" t="n">
-        <v>0.602459</v>
+        <v>0.659649</v>
       </c>
     </row>
     <row r="385">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.018229</v>
+        <v>0.032673</v>
       </c>
       <c r="C385" t="n">
-        <v>0.598361</v>
+        <v>0.6561399999999999</v>
       </c>
     </row>
     <row r="386">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.018243</v>
+        <v>0.032726</v>
       </c>
       <c r="C386" t="n">
-        <v>0.594262</v>
+        <v>0.652632</v>
       </c>
     </row>
     <row r="387">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.01825</v>
+        <v>0.033323</v>
       </c>
       <c r="C387" t="n">
-        <v>0.590164</v>
+        <v>0.649123</v>
       </c>
     </row>
     <row r="388">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.018398</v>
+        <v>0.033696</v>
       </c>
       <c r="C388" t="n">
-        <v>0.586066</v>
+        <v>0.645614</v>
       </c>
     </row>
     <row r="389">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.018542</v>
+        <v>0.034174</v>
       </c>
       <c r="C389" t="n">
-        <v>0.581967</v>
+        <v>0.642105</v>
       </c>
     </row>
     <row r="390">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.019095</v>
+        <v>0.034558</v>
       </c>
       <c r="C390" t="n">
-        <v>0.577869</v>
+        <v>0.6385960000000001</v>
       </c>
     </row>
     <row r="391">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.019584</v>
+        <v>0.034629</v>
       </c>
       <c r="C391" t="n">
-        <v>0.57377</v>
+        <v>0.635088</v>
       </c>
     </row>
     <row r="392">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.020031</v>
+        <v>0.035485</v>
       </c>
       <c r="C392" t="n">
-        <v>0.569672</v>
+        <v>0.631579</v>
       </c>
     </row>
     <row r="393">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.020092</v>
+        <v>0.035517</v>
       </c>
       <c r="C393" t="n">
-        <v>0.565574</v>
+        <v>0.62807</v>
       </c>
     </row>
     <row r="394">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.020604</v>
+        <v>0.035527</v>
       </c>
       <c r="C394" t="n">
-        <v>0.5614749999999999</v>
+        <v>0.624561</v>
       </c>
     </row>
     <row r="395">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.020888</v>
+        <v>0.036056</v>
       </c>
       <c r="C395" t="n">
-        <v>0.557377</v>
+        <v>0.621053</v>
       </c>
     </row>
     <row r="396">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.021179</v>
+        <v>0.036549</v>
       </c>
       <c r="C396" t="n">
-        <v>0.553279</v>
+        <v>0.617544</v>
       </c>
     </row>
     <row r="397">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.021466</v>
+        <v>0.036625</v>
       </c>
       <c r="C397" t="n">
-        <v>0.54918</v>
+        <v>0.614035</v>
       </c>
     </row>
     <row r="398">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.021824</v>
+        <v>0.037059</v>
       </c>
       <c r="C398" t="n">
-        <v>0.545082</v>
+        <v>0.610526</v>
       </c>
     </row>
     <row r="399">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.02201</v>
+        <v>0.037395</v>
       </c>
       <c r="C399" t="n">
-        <v>0.540984</v>
+        <v>0.6070179999999999</v>
       </c>
     </row>
     <row r="400">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.02222</v>
+        <v>0.037468</v>
       </c>
       <c r="C400" t="n">
-        <v>0.5368849999999999</v>
+        <v>0.603509</v>
       </c>
     </row>
     <row r="401">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.022221</v>
+        <v>0.037835</v>
       </c>
       <c r="C401" t="n">
-        <v>0.532787</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="402">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.022503</v>
+        <v>0.038032</v>
       </c>
       <c r="C402" t="n">
-        <v>0.528689</v>
+        <v>0.596491</v>
       </c>
     </row>
     <row r="403">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.022981</v>
+        <v>0.038672</v>
       </c>
       <c r="C403" t="n">
-        <v>0.52459</v>
+        <v>0.592982</v>
       </c>
     </row>
     <row r="404">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.023172</v>
+        <v>0.03951</v>
       </c>
       <c r="C404" t="n">
-        <v>0.520492</v>
+        <v>0.5894740000000001</v>
       </c>
     </row>
     <row r="405">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.023193</v>
+        <v>0.039767</v>
       </c>
       <c r="C405" t="n">
-        <v>0.516393</v>
+        <v>0.585965</v>
       </c>
     </row>
     <row r="406">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.023226</v>
+        <v>0.039903</v>
       </c>
       <c r="C406" t="n">
-        <v>0.5122949999999999</v>
+        <v>0.582456</v>
       </c>
     </row>
     <row r="407">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.023258</v>
+        <v>0.040072</v>
       </c>
       <c r="C407" t="n">
-        <v>0.508197</v>
+        <v>0.578947</v>
       </c>
     </row>
     <row r="408">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.023271</v>
+        <v>0.040342</v>
       </c>
       <c r="C408" t="n">
-        <v>0.504098</v>
+        <v>0.575439</v>
       </c>
     </row>
     <row r="409">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.02376</v>
+        <v>0.040805</v>
       </c>
       <c r="C409" t="n">
-        <v>0.5</v>
+        <v>0.57193</v>
       </c>
     </row>
     <row r="410">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.023897</v>
+        <v>0.041108</v>
       </c>
       <c r="C410" t="n">
-        <v>0.495902</v>
+        <v>0.568421</v>
       </c>
     </row>
     <row r="411">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.023961</v>
+        <v>0.04122</v>
       </c>
       <c r="C411" t="n">
-        <v>0.491803</v>
+        <v>0.564912</v>
       </c>
     </row>
     <row r="412">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.02398</v>
+        <v>0.041263</v>
       </c>
       <c r="C412" t="n">
-        <v>0.487705</v>
+        <v>0.561404</v>
       </c>
     </row>
     <row r="413">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.02399</v>
+        <v>0.041829</v>
       </c>
       <c r="C413" t="n">
-        <v>0.483607</v>
+        <v>0.557895</v>
       </c>
     </row>
     <row r="414">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.024443</v>
+        <v>0.041927</v>
       </c>
       <c r="C414" t="n">
-        <v>0.479508</v>
+        <v>0.554386</v>
       </c>
     </row>
     <row r="415">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.024993</v>
+        <v>0.042393</v>
       </c>
       <c r="C415" t="n">
-        <v>0.47541</v>
+        <v>0.550877</v>
       </c>
     </row>
     <row r="416">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.02528</v>
+        <v>0.042448</v>
       </c>
       <c r="C416" t="n">
-        <v>0.471311</v>
+        <v>0.547368</v>
       </c>
     </row>
     <row r="417">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.025346</v>
+        <v>0.042549</v>
       </c>
       <c r="C417" t="n">
-        <v>0.467213</v>
+        <v>0.54386</v>
       </c>
     </row>
     <row r="418">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.025712</v>
+        <v>0.042584</v>
       </c>
       <c r="C418" t="n">
-        <v>0.463115</v>
+        <v>0.540351</v>
       </c>
     </row>
     <row r="419">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.02577</v>
+        <v>0.042598</v>
       </c>
       <c r="C419" t="n">
-        <v>0.459016</v>
+        <v>0.536842</v>
       </c>
     </row>
     <row r="420">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.02609</v>
+        <v>0.042866</v>
       </c>
       <c r="C420" t="n">
-        <v>0.454918</v>
+        <v>0.5333329999999999</v>
       </c>
     </row>
     <row r="421">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.026798</v>
+        <v>0.042883</v>
       </c>
       <c r="C421" t="n">
-        <v>0.45082</v>
+        <v>0.529825</v>
       </c>
     </row>
     <row r="422">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.027314</v>
+        <v>0.044075</v>
       </c>
       <c r="C422" t="n">
-        <v>0.446721</v>
+        <v>0.526316</v>
       </c>
     </row>
     <row r="423">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.027723</v>
+        <v>0.044079</v>
       </c>
       <c r="C423" t="n">
-        <v>0.442623</v>
+        <v>0.522807</v>
       </c>
     </row>
     <row r="424">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.027802</v>
+        <v>0.044848</v>
       </c>
       <c r="C424" t="n">
-        <v>0.438525</v>
+        <v>0.519298</v>
       </c>
     </row>
     <row r="425">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.028129</v>
+        <v>0.045071</v>
       </c>
       <c r="C425" t="n">
-        <v>0.434426</v>
+        <v>0.5157890000000001</v>
       </c>
     </row>
     <row r="426">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.028195</v>
+        <v>0.045173</v>
       </c>
       <c r="C426" t="n">
-        <v>0.430328</v>
+        <v>0.512281</v>
       </c>
     </row>
     <row r="427">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.028412</v>
+        <v>0.04552</v>
       </c>
       <c r="C427" t="n">
-        <v>0.42623</v>
+        <v>0.508772</v>
       </c>
     </row>
     <row r="428">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.028669</v>
+        <v>0.046123</v>
       </c>
       <c r="C428" t="n">
-        <v>0.422131</v>
+        <v>0.505263</v>
       </c>
     </row>
     <row r="429">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.029301</v>
+        <v>0.046465</v>
       </c>
       <c r="C429" t="n">
-        <v>0.418033</v>
+        <v>0.501754</v>
       </c>
     </row>
     <row r="430">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.029451</v>
+        <v>0.047002</v>
       </c>
       <c r="C430" t="n">
-        <v>0.413934</v>
+        <v>0.498246</v>
       </c>
     </row>
     <row r="431">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.030135</v>
+        <v>0.047089</v>
       </c>
       <c r="C431" t="n">
-        <v>0.409836</v>
+        <v>0.494737</v>
       </c>
     </row>
     <row r="432">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.030577</v>
+        <v>0.047436</v>
       </c>
       <c r="C432" t="n">
-        <v>0.405738</v>
+        <v>0.491228</v>
       </c>
     </row>
     <row r="433">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.030811</v>
+        <v>0.04761</v>
       </c>
       <c r="C433" t="n">
-        <v>0.401639</v>
+        <v>0.487719</v>
       </c>
     </row>
     <row r="434">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.031138</v>
+        <v>0.048053</v>
       </c>
       <c r="C434" t="n">
-        <v>0.397541</v>
+        <v>0.484211</v>
       </c>
     </row>
     <row r="435">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.031735</v>
+        <v>0.048983</v>
       </c>
       <c r="C435" t="n">
-        <v>0.393443</v>
+        <v>0.480702</v>
       </c>
     </row>
     <row r="436">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.031886</v>
+        <v>0.049112</v>
       </c>
       <c r="C436" t="n">
-        <v>0.389344</v>
+        <v>0.477193</v>
       </c>
     </row>
     <row r="437">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.032194</v>
+        <v>0.049273</v>
       </c>
       <c r="C437" t="n">
-        <v>0.385246</v>
+        <v>0.473684</v>
       </c>
     </row>
     <row r="438">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.03254</v>
+        <v>0.049723</v>
       </c>
       <c r="C438" t="n">
-        <v>0.381148</v>
+        <v>0.470175</v>
       </c>
     </row>
     <row r="439">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.032643</v>
+        <v>0.050154</v>
       </c>
       <c r="C439" t="n">
-        <v>0.377049</v>
+        <v>0.466667</v>
       </c>
     </row>
     <row r="440">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.03273</v>
+        <v>0.050377</v>
       </c>
       <c r="C440" t="n">
-        <v>0.372951</v>
+        <v>0.463158</v>
       </c>
     </row>
     <row r="441">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.033701</v>
+        <v>0.05078</v>
       </c>
       <c r="C441" t="n">
-        <v>0.368852</v>
+        <v>0.459649</v>
       </c>
     </row>
     <row r="442">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.034223</v>
+        <v>0.0508</v>
       </c>
       <c r="C442" t="n">
-        <v>0.364754</v>
+        <v>0.45614</v>
       </c>
     </row>
     <row r="443">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.03423</v>
+        <v>0.051353</v>
       </c>
       <c r="C443" t="n">
-        <v>0.360656</v>
+        <v>0.452632</v>
       </c>
     </row>
     <row r="444">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.034248</v>
+        <v>0.051734</v>
       </c>
       <c r="C444" t="n">
-        <v>0.356557</v>
+        <v>0.449123</v>
       </c>
     </row>
     <row r="445">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.03438</v>
+        <v>0.051824</v>
       </c>
       <c r="C445" t="n">
-        <v>0.352459</v>
+        <v>0.445614</v>
       </c>
     </row>
     <row r="446">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.034906</v>
+        <v>0.051859</v>
       </c>
       <c r="C446" t="n">
-        <v>0.348361</v>
+        <v>0.442105</v>
       </c>
     </row>
     <row r="447">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.034937</v>
+        <v>0.052258</v>
       </c>
       <c r="C447" t="n">
-        <v>0.344262</v>
+        <v>0.438596</v>
       </c>
     </row>
     <row r="448">
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.035154</v>
+        <v>0.052694</v>
       </c>
       <c r="C448" t="n">
-        <v>0.340164</v>
+        <v>0.435088</v>
       </c>
     </row>
     <row r="449">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.035182</v>
+        <v>0.052855</v>
       </c>
       <c r="C449" t="n">
-        <v>0.336066</v>
+        <v>0.431579</v>
       </c>
     </row>
     <row r="450">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.035592</v>
+        <v>0.053096</v>
       </c>
       <c r="C450" t="n">
-        <v>0.331967</v>
+        <v>0.42807</v>
       </c>
     </row>
     <row r="451">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.035959</v>
+        <v>0.053417</v>
       </c>
       <c r="C451" t="n">
-        <v>0.327869</v>
+        <v>0.424561</v>
       </c>
     </row>
     <row r="452">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.036072</v>
+        <v>0.054588</v>
       </c>
       <c r="C452" t="n">
-        <v>0.32377</v>
+        <v>0.421053</v>
       </c>
     </row>
     <row r="453">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.036163</v>
+        <v>0.0576</v>
       </c>
       <c r="C453" t="n">
-        <v>0.319672</v>
+        <v>0.417544</v>
       </c>
     </row>
     <row r="454">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.036307</v>
+        <v>0.057988</v>
       </c>
       <c r="C454" t="n">
-        <v>0.315574</v>
+        <v>0.414035</v>
       </c>
     </row>
     <row r="455">
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.036858</v>
+        <v>0.059035</v>
       </c>
       <c r="C455" t="n">
-        <v>0.311475</v>
+        <v>0.410526</v>
       </c>
     </row>
     <row r="456">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.037193</v>
+        <v>0.059554</v>
       </c>
       <c r="C456" t="n">
-        <v>0.307377</v>
+        <v>0.407018</v>
       </c>
     </row>
     <row r="457">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.038055</v>
+        <v>0.059931</v>
       </c>
       <c r="C457" t="n">
-        <v>0.303279</v>
+        <v>0.403509</v>
       </c>
     </row>
     <row r="458">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.038963</v>
+        <v>0.060434</v>
       </c>
       <c r="C458" t="n">
-        <v>0.29918</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="459">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.039012</v>
+        <v>0.060581</v>
       </c>
       <c r="C459" t="n">
-        <v>0.295082</v>
+        <v>0.396491</v>
       </c>
     </row>
     <row r="460">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.039137</v>
+        <v>0.061049</v>
       </c>
       <c r="C460" t="n">
-        <v>0.290984</v>
+        <v>0.392982</v>
       </c>
     </row>
     <row r="461">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.039154</v>
+        <v>0.061278</v>
       </c>
       <c r="C461" t="n">
-        <v>0.286885</v>
+        <v>0.389474</v>
       </c>
     </row>
     <row r="462">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.039933</v>
+        <v>0.06162</v>
       </c>
       <c r="C462" t="n">
-        <v>0.282787</v>
+        <v>0.385965</v>
       </c>
     </row>
     <row r="463">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.040119</v>
+        <v>0.061908</v>
       </c>
       <c r="C463" t="n">
-        <v>0.278689</v>
+        <v>0.382456</v>
       </c>
     </row>
     <row r="464">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.040357</v>
+        <v>0.062292</v>
       </c>
       <c r="C464" t="n">
-        <v>0.27459</v>
+        <v>0.378947</v>
       </c>
     </row>
     <row r="465">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.040711</v>
+        <v>0.06237</v>
       </c>
       <c r="C465" t="n">
-        <v>0.270492</v>
+        <v>0.375439</v>
       </c>
     </row>
     <row r="466">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.04127</v>
+        <v>0.062478</v>
       </c>
       <c r="C466" t="n">
-        <v>0.266393</v>
+        <v>0.37193</v>
       </c>
     </row>
     <row r="467">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.042031</v>
+        <v>0.06293600000000001</v>
       </c>
       <c r="C467" t="n">
-        <v>0.262295</v>
+        <v>0.368421</v>
       </c>
     </row>
     <row r="468">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.042773</v>
+        <v>0.06336</v>
       </c>
       <c r="C468" t="n">
-        <v>0.258197</v>
+        <v>0.364912</v>
       </c>
     </row>
     <row r="469">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.042968</v>
+        <v>0.065238</v>
       </c>
       <c r="C469" t="n">
-        <v>0.254098</v>
+        <v>0.361404</v>
       </c>
     </row>
     <row r="470">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.043509</v>
+        <v>0.065677</v>
       </c>
       <c r="C470" t="n">
-        <v>0.25</v>
+        <v>0.357895</v>
       </c>
     </row>
     <row r="471">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.04454</v>
+        <v>0.065734</v>
       </c>
       <c r="C471" t="n">
-        <v>0.245902</v>
+        <v>0.354386</v>
       </c>
     </row>
     <row r="472">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.045225</v>
+        <v>0.06701699999999999</v>
       </c>
       <c r="C472" t="n">
-        <v>0.241803</v>
+        <v>0.350877</v>
       </c>
     </row>
     <row r="473">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.045447</v>
+        <v>0.067551</v>
       </c>
       <c r="C473" t="n">
-        <v>0.237705</v>
+        <v>0.347368</v>
       </c>
     </row>
     <row r="474">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.04692</v>
+        <v>0.06758400000000001</v>
       </c>
       <c r="C474" t="n">
-        <v>0.233607</v>
+        <v>0.34386</v>
       </c>
     </row>
     <row r="475">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.048464</v>
+        <v>0.068353</v>
       </c>
       <c r="C475" t="n">
-        <v>0.229508</v>
+        <v>0.340351</v>
       </c>
     </row>
     <row r="476">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.049449</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C476" t="n">
-        <v>0.22541</v>
+        <v>0.336842</v>
       </c>
     </row>
     <row r="477">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.050122</v>
+        <v>0.06900100000000001</v>
       </c>
       <c r="C477" t="n">
-        <v>0.221311</v>
+        <v>0.333333</v>
       </c>
     </row>
     <row r="478">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.050723</v>
+        <v>0.07023600000000001</v>
       </c>
       <c r="C478" t="n">
-        <v>0.217213</v>
+        <v>0.329825</v>
       </c>
     </row>
     <row r="479">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.05193</v>
+        <v>0.07054100000000001</v>
       </c>
       <c r="C479" t="n">
-        <v>0.213115</v>
+        <v>0.326316</v>
       </c>
     </row>
     <row r="480">
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.053408</v>
+        <v>0.070783</v>
       </c>
       <c r="C480" t="n">
-        <v>0.209016</v>
+        <v>0.322807</v>
       </c>
     </row>
     <row r="481">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.054243</v>
+        <v>0.07180300000000001</v>
       </c>
       <c r="C481" t="n">
-        <v>0.204918</v>
+        <v>0.319298</v>
       </c>
     </row>
     <row r="482">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.054642</v>
+        <v>0.07199700000000001</v>
       </c>
       <c r="C482" t="n">
-        <v>0.20082</v>
+        <v>0.315789</v>
       </c>
     </row>
     <row r="483">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.054677</v>
+        <v>0.07201200000000001</v>
       </c>
       <c r="C483" t="n">
-        <v>0.196721</v>
+        <v>0.312281</v>
       </c>
     </row>
     <row r="484">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.054682</v>
+        <v>0.07216599999999999</v>
       </c>
       <c r="C484" t="n">
-        <v>0.192623</v>
+        <v>0.308772</v>
       </c>
     </row>
     <row r="485">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.055605</v>
+        <v>0.07248</v>
       </c>
       <c r="C485" t="n">
-        <v>0.188525</v>
+        <v>0.305263</v>
       </c>
     </row>
     <row r="486">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.055947</v>
+        <v>0.072501</v>
       </c>
       <c r="C486" t="n">
-        <v>0.184426</v>
+        <v>0.301754</v>
       </c>
     </row>
     <row r="487">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.056187</v>
+        <v>0.07272199999999999</v>
       </c>
       <c r="C487" t="n">
-        <v>0.180328</v>
+        <v>0.298246</v>
       </c>
     </row>
     <row r="488">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.057511</v>
+        <v>0.072922</v>
       </c>
       <c r="C488" t="n">
-        <v>0.17623</v>
+        <v>0.294737</v>
       </c>
     </row>
     <row r="489">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.05775</v>
+        <v>0.072994</v>
       </c>
       <c r="C489" t="n">
-        <v>0.172131</v>
+        <v>0.291228</v>
       </c>
     </row>
     <row r="490">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.059273</v>
+        <v>0.073312</v>
       </c>
       <c r="C490" t="n">
-        <v>0.168033</v>
+        <v>0.287719</v>
       </c>
     </row>
     <row r="491">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.059938</v>
+        <v>0.073904</v>
       </c>
       <c r="C491" t="n">
-        <v>0.163934</v>
+        <v>0.284211</v>
       </c>
     </row>
     <row r="492">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.064294</v>
+        <v>0.074253</v>
       </c>
       <c r="C492" t="n">
-        <v>0.159836</v>
+        <v>0.280702</v>
       </c>
     </row>
     <row r="493">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.06469800000000001</v>
+        <v>0.07434399999999999</v>
       </c>
       <c r="C493" t="n">
-        <v>0.155738</v>
+        <v>0.277193</v>
       </c>
     </row>
     <row r="494">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.06568599999999999</v>
+        <v>0.074932</v>
       </c>
       <c r="C494" t="n">
-        <v>0.151639</v>
+        <v>0.273684</v>
       </c>
     </row>
     <row r="495">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.069674</v>
+        <v>0.07549</v>
       </c>
       <c r="C495" t="n">
-        <v>0.147541</v>
+        <v>0.270175</v>
       </c>
     </row>
     <row r="496">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.069978</v>
+        <v>0.079542</v>
       </c>
       <c r="C496" t="n">
-        <v>0.143443</v>
+        <v>0.266667</v>
       </c>
     </row>
     <row r="497">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.072381</v>
+        <v>0.079663</v>
       </c>
       <c r="C497" t="n">
-        <v>0.139344</v>
+        <v>0.263158</v>
       </c>
     </row>
     <row r="498">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.073</v>
+        <v>0.080985</v>
       </c>
       <c r="C498" t="n">
-        <v>0.135246</v>
+        <v>0.259649</v>
       </c>
     </row>
     <row r="499">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.07517</v>
+        <v>0.081458</v>
       </c>
       <c r="C499" t="n">
-        <v>0.131148</v>
+        <v>0.25614</v>
       </c>
     </row>
     <row r="500">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.075423</v>
+        <v>0.083244</v>
       </c>
       <c r="C500" t="n">
-        <v>0.127049</v>
+        <v>0.252632</v>
       </c>
     </row>
     <row r="501">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.075562</v>
+        <v>0.083772</v>
       </c>
       <c r="C501" t="n">
-        <v>0.122951</v>
+        <v>0.249123</v>
       </c>
     </row>
     <row r="502">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.07824399999999999</v>
+        <v>0.08411</v>
       </c>
       <c r="C502" t="n">
-        <v>0.118852</v>
+        <v>0.245614</v>
       </c>
     </row>
     <row r="503">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.078717</v>
+        <v>0.084355</v>
       </c>
       <c r="C503" t="n">
-        <v>0.114754</v>
+        <v>0.242105</v>
       </c>
     </row>
     <row r="504">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.07914499999999999</v>
+        <v>0.08479100000000001</v>
       </c>
       <c r="C504" t="n">
-        <v>0.110656</v>
+        <v>0.238596</v>
       </c>
     </row>
     <row r="505">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.081695</v>
+        <v>0.085094</v>
       </c>
       <c r="C505" t="n">
-        <v>0.106557</v>
+        <v>0.235088</v>
       </c>
     </row>
     <row r="506">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.082123</v>
+        <v>0.08670799999999999</v>
       </c>
       <c r="C506" t="n">
-        <v>0.102459</v>
+        <v>0.231579</v>
       </c>
     </row>
     <row r="507">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.084413</v>
+        <v>0.087604</v>
       </c>
       <c r="C507" t="n">
-        <v>0.098361</v>
+        <v>0.22807</v>
       </c>
     </row>
     <row r="508">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.084914</v>
+        <v>0.08996999999999999</v>
       </c>
       <c r="C508" t="n">
-        <v>0.094262</v>
+        <v>0.224561</v>
       </c>
     </row>
     <row r="509">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.09186999999999999</v>
+        <v>0.090321</v>
       </c>
       <c r="C509" t="n">
-        <v>0.09016399999999999</v>
+        <v>0.221053</v>
       </c>
     </row>
     <row r="510">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.09209100000000001</v>
+        <v>0.090488</v>
       </c>
       <c r="C510" t="n">
-        <v>0.086066</v>
+        <v>0.217544</v>
       </c>
     </row>
     <row r="511">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.095711</v>
+        <v>0.090684</v>
       </c>
       <c r="C511" t="n">
-        <v>0.081967</v>
+        <v>0.214035</v>
       </c>
     </row>
     <row r="512">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.09672699999999999</v>
+        <v>0.09341000000000001</v>
       </c>
       <c r="C512" t="n">
-        <v>0.07786899999999999</v>
+        <v>0.210526</v>
       </c>
     </row>
     <row r="513">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.100475</v>
+        <v>0.09364400000000001</v>
       </c>
       <c r="C513" t="n">
-        <v>0.07377</v>
+        <v>0.207018</v>
       </c>
     </row>
     <row r="514">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.103932</v>
+        <v>0.094628</v>
       </c>
       <c r="C514" t="n">
-        <v>0.069672</v>
+        <v>0.203509</v>
       </c>
     </row>
     <row r="515">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.105349</v>
+        <v>0.09479799999999999</v>
       </c>
       <c r="C515" t="n">
-        <v>0.06557399999999999</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="516">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.109188</v>
+        <v>0.09540800000000001</v>
       </c>
       <c r="C516" t="n">
-        <v>0.061475</v>
+        <v>0.196491</v>
       </c>
     </row>
     <row r="517">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.110052</v>
+        <v>0.09744</v>
       </c>
       <c r="C517" t="n">
-        <v>0.057377</v>
+        <v>0.192982</v>
       </c>
     </row>
     <row r="518">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.117282</v>
+        <v>0.098304</v>
       </c>
       <c r="C518" t="n">
-        <v>0.053279</v>
+        <v>0.189474</v>
       </c>
     </row>
     <row r="519">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.122239</v>
+        <v>0.100853</v>
       </c>
       <c r="C519" t="n">
-        <v>0.04918</v>
+        <v>0.185965</v>
       </c>
     </row>
     <row r="520">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.124275</v>
+        <v>0.101501</v>
       </c>
       <c r="C520" t="n">
-        <v>0.045082</v>
+        <v>0.182456</v>
       </c>
     </row>
     <row r="521">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.125127</v>
+        <v>0.101815</v>
       </c>
       <c r="C521" t="n">
-        <v>0.040984</v>
+        <v>0.178947</v>
       </c>
     </row>
     <row r="522">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.136168</v>
+        <v>0.104641</v>
       </c>
       <c r="C522" t="n">
-        <v>0.036885</v>
+        <v>0.175439</v>
       </c>
     </row>
     <row r="523">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.157401</v>
+        <v>0.10635</v>
       </c>
       <c r="C523" t="n">
-        <v>0.032787</v>
+        <v>0.17193</v>
       </c>
     </row>
     <row r="524">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.168227</v>
+        <v>0.107437</v>
       </c>
       <c r="C524" t="n">
-        <v>0.028689</v>
+        <v>0.168421</v>
       </c>
     </row>
     <row r="525">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.246573</v>
+        <v>0.109914</v>
       </c>
       <c r="C525" t="n">
-        <v>0.02459</v>
+        <v>0.164912</v>
       </c>
     </row>
     <row r="526">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.26908</v>
+        <v>0.113696</v>
       </c>
       <c r="C526" t="n">
-        <v>0.020492</v>
+        <v>0.161404</v>
       </c>
     </row>
     <row r="527">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.282467</v>
+        <v>0.116878</v>
       </c>
       <c r="C527" t="n">
-        <v>0.016393</v>
+        <v>0.157895</v>
       </c>
     </row>
     <row r="528">
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.29084</v>
+        <v>0.118922</v>
       </c>
       <c r="C528" t="n">
-        <v>0.012295</v>
+        <v>0.154386</v>
       </c>
     </row>
     <row r="529">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.310317</v>
+        <v>0.119417</v>
       </c>
       <c r="C529" t="n">
-        <v>0.008196999999999999</v>
+        <v>0.150877</v>
       </c>
     </row>
     <row r="530">
@@ -7304,10 +7304,543 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.424287</v>
+        <v>0.122195</v>
       </c>
       <c r="C530" t="n">
-        <v>0.004098</v>
+        <v>0.147368</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0.122416</v>
+      </c>
+      <c r="C531" t="n">
+        <v>0.14386</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>0.122651</v>
+      </c>
+      <c r="C532" t="n">
+        <v>0.140351</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>0.122933</v>
+      </c>
+      <c r="C533" t="n">
+        <v>0.136842</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>0.123213</v>
+      </c>
+      <c r="C534" t="n">
+        <v>0.133333</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>0.126332</v>
+      </c>
+      <c r="C535" t="n">
+        <v>0.129825</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="C536" t="n">
+        <v>0.126316</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0.132711</v>
+      </c>
+      <c r="C537" t="n">
+        <v>0.122807</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>0.133638</v>
+      </c>
+      <c r="C538" t="n">
+        <v>0.119298</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>0.133821</v>
+      </c>
+      <c r="C539" t="n">
+        <v>0.115789</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>0.135713</v>
+      </c>
+      <c r="C540" t="n">
+        <v>0.112281</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>0.136769</v>
+      </c>
+      <c r="C541" t="n">
+        <v>0.108772</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>0.137899</v>
+      </c>
+      <c r="C542" t="n">
+        <v>0.105263</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.138687</v>
+      </c>
+      <c r="C543" t="n">
+        <v>0.101754</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.14186</v>
+      </c>
+      <c r="C544" t="n">
+        <v>0.098246</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>0.148286</v>
+      </c>
+      <c r="C545" t="n">
+        <v>0.094737</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>0.151501</v>
+      </c>
+      <c r="C546" t="n">
+        <v>0.091228</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>0.152715</v>
+      </c>
+      <c r="C547" t="n">
+        <v>0.08771900000000001</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>0.155988</v>
+      </c>
+      <c r="C548" t="n">
+        <v>0.08421099999999999</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>0.157998</v>
+      </c>
+      <c r="C549" t="n">
+        <v>0.080702</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>0.160496</v>
+      </c>
+      <c r="C550" t="n">
+        <v>0.077193</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>0.176604</v>
+      </c>
+      <c r="C551" t="n">
+        <v>0.073684</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0.178572</v>
+      </c>
+      <c r="C552" t="n">
+        <v>0.070175</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>0.180767</v>
+      </c>
+      <c r="C553" t="n">
+        <v>0.066667</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>0.180831</v>
+      </c>
+      <c r="C554" t="n">
+        <v>0.06315800000000001</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>0.181706</v>
+      </c>
+      <c r="C555" t="n">
+        <v>0.059649</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>0.188004</v>
+      </c>
+      <c r="C556" t="n">
+        <v>0.05614</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>0.203962</v>
+      </c>
+      <c r="C557" t="n">
+        <v>0.052632</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>0.218074</v>
+      </c>
+      <c r="C558" t="n">
+        <v>0.049123</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>0.243699</v>
+      </c>
+      <c r="C559" t="n">
+        <v>0.045614</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>0.245528</v>
+      </c>
+      <c r="C560" t="n">
+        <v>0.042105</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>0.265446</v>
+      </c>
+      <c r="C561" t="n">
+        <v>0.038596</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>0.299569</v>
+      </c>
+      <c r="C562" t="n">
+        <v>0.035088</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>0.317172</v>
+      </c>
+      <c r="C563" t="n">
+        <v>0.031579</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>0.336181</v>
+      </c>
+      <c r="C564" t="n">
+        <v>0.02807</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>0.363331</v>
+      </c>
+      <c r="C565" t="n">
+        <v>0.024561</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>0.397879</v>
+      </c>
+      <c r="C566" t="n">
+        <v>0.021053</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>0.410881</v>
+      </c>
+      <c r="C567" t="n">
+        <v>0.017544</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>0.535842</v>
+      </c>
+      <c r="C568" t="n">
+        <v>0.014035</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.682508</v>
+      </c>
+      <c r="C569" t="n">
+        <v>0.010526</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>0.958378</v>
+      </c>
+      <c r="C570" t="n">
+        <v>0.007018</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Adjusted target</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>0.968929</v>
+      </c>
+      <c r="C571" t="n">
+        <v>0.003509</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.000111</v>
+        <v>0.000112</v>
       </c>
       <c r="C456" t="n">
         <v>0.997792</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.000456</v>
+        <v>0.000432</v>
       </c>
       <c r="C457" t="n">
         <v>0.9955850000000001</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.00052</v>
+        <v>0.000522</v>
       </c>
       <c r="C459" t="n">
         <v>0.99117</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.0009890000000000001</v>
+        <v>0.000976</v>
       </c>
       <c r="C460" t="n">
         <v>0.988962</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.001064</v>
+        <v>0.001075</v>
       </c>
       <c r="C461" t="n">
         <v>0.986755</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.001642</v>
+        <v>0.00163</v>
       </c>
       <c r="C462" t="n">
         <v>0.9845469999999999</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.001909</v>
+        <v>0.001907</v>
       </c>
       <c r="C463" t="n">
         <v>0.98234</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.002006</v>
+        <v>0.002026</v>
       </c>
       <c r="C464" t="n">
         <v>0.980132</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.002387</v>
+        <v>0.00237</v>
       </c>
       <c r="C465" t="n">
         <v>0.977925</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.002521</v>
+        <v>0.002467</v>
       </c>
       <c r="C466" t="n">
         <v>0.9757169999999999</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.002719</v>
+        <v>0.00273</v>
       </c>
       <c r="C467" t="n">
         <v>0.97351</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.002825</v>
+        <v>0.002863</v>
       </c>
       <c r="C468" t="n">
         <v>0.971302</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.003072</v>
+        <v>0.003041</v>
       </c>
       <c r="C469" t="n">
         <v>0.969095</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.003244</v>
+        <v>0.003083</v>
       </c>
       <c r="C470" t="n">
         <v>0.9668870000000001</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.00347</v>
+        <v>0.003427</v>
       </c>
       <c r="C471" t="n">
         <v>0.96468</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.003797</v>
+        <v>0.003746</v>
       </c>
       <c r="C472" t="n">
         <v>0.962472</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.003917</v>
+        <v>0.003904</v>
       </c>
       <c r="C473" t="n">
         <v>0.960265</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.004209</v>
+        <v>0.00422</v>
       </c>
       <c r="C475" t="n">
         <v>0.95585</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.004334</v>
+        <v>0.004338</v>
       </c>
       <c r="C476" t="n">
         <v>0.953642</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.004483</v>
+        <v>0.004494</v>
       </c>
       <c r="C477" t="n">
         <v>0.951435</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.004516</v>
+        <v>0.004502</v>
       </c>
       <c r="C478" t="n">
         <v>0.949227</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.004699</v>
+        <v>0.004602</v>
       </c>
       <c r="C479" t="n">
         <v>0.94702</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.004784</v>
+        <v>0.004624</v>
       </c>
       <c r="C480" t="n">
         <v>0.944812</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.004812</v>
+        <v>0.00464</v>
       </c>
       <c r="C481" t="n">
         <v>0.942605</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.004923</v>
+        <v>0.004714</v>
       </c>
       <c r="C482" t="n">
         <v>0.940397</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.00493</v>
+        <v>0.00482</v>
       </c>
       <c r="C483" t="n">
         <v>0.93819</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.004946</v>
+        <v>0.004869</v>
       </c>
       <c r="C484" t="n">
         <v>0.935982</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.00509</v>
+        <v>0.004905</v>
       </c>
       <c r="C485" t="n">
         <v>0.933775</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.005219</v>
+        <v>0.005207</v>
       </c>
       <c r="C486" t="n">
         <v>0.931567</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.005569</v>
+        <v>0.005361</v>
       </c>
       <c r="C487" t="n">
         <v>0.92936</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.005575</v>
+        <v>0.00568</v>
       </c>
       <c r="C488" t="n">
         <v>0.927152</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.005686</v>
+        <v>0.005687</v>
       </c>
       <c r="C489" t="n">
         <v>0.924945</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.005702</v>
+        <v>0.00572</v>
       </c>
       <c r="C490" t="n">
         <v>0.922737</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.005814</v>
+        <v>0.005739</v>
       </c>
       <c r="C491" t="n">
         <v>0.92053</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.006171</v>
+        <v>0.005825</v>
       </c>
       <c r="C492" t="n">
         <v>0.918322</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.007702</v>
+        <v>0.007171</v>
       </c>
       <c r="C493" t="n">
         <v>0.916115</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.008129000000000001</v>
+        <v>0.007697</v>
       </c>
       <c r="C494" t="n">
         <v>0.913907</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.008227</v>
+        <v>0.008056000000000001</v>
       </c>
       <c r="C495" t="n">
         <v>0.9117</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.008439</v>
+        <v>0.008225</v>
       </c>
       <c r="C496" t="n">
         <v>0.909492</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.008742</v>
+        <v>0.00847</v>
       </c>
       <c r="C497" t="n">
         <v>0.907285</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.008926</v>
+        <v>0.008989</v>
       </c>
       <c r="C498" t="n">
         <v>0.905077</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.009280999999999999</v>
+        <v>0.009213000000000001</v>
       </c>
       <c r="C499" t="n">
         <v>0.90287</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.009313</v>
+        <v>0.009220000000000001</v>
       </c>
       <c r="C500" t="n">
         <v>0.900662</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.009443</v>
+        <v>0.009414</v>
       </c>
       <c r="C501" t="n">
         <v>0.898455</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.009547</v>
+        <v>0.009436999999999999</v>
       </c>
       <c r="C502" t="n">
         <v>0.896247</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.009763000000000001</v>
+        <v>0.009525</v>
       </c>
       <c r="C503" t="n">
         <v>0.8940399999999999</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.009946999999999999</v>
+        <v>0.009572000000000001</v>
       </c>
       <c r="C504" t="n">
         <v>0.891832</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.009962</v>
+        <v>0.009853000000000001</v>
       </c>
       <c r="C505" t="n">
         <v>0.889625</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.010013</v>
+        <v>0.009953</v>
       </c>
       <c r="C506" t="n">
         <v>0.887417</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.010026</v>
+        <v>0.010006</v>
       </c>
       <c r="C507" t="n">
         <v>0.8852100000000001</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.010412</v>
+        <v>0.010053</v>
       </c>
       <c r="C508" t="n">
         <v>0.883002</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.010732</v>
+        <v>0.010508</v>
       </c>
       <c r="C509" t="n">
         <v>0.880795</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.010882</v>
+        <v>0.010817</v>
       </c>
       <c r="C510" t="n">
         <v>0.878587</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.010928</v>
+        <v>0.010932</v>
       </c>
       <c r="C511" t="n">
         <v>0.87638</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.010946</v>
+        <v>0.01095</v>
       </c>
       <c r="C512" t="n">
         <v>0.8741719999999999</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.011175</v>
+        <v>0.01105</v>
       </c>
       <c r="C513" t="n">
         <v>0.871965</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.011279</v>
+        <v>0.01123</v>
       </c>
       <c r="C514" t="n">
         <v>0.869757</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.011319</v>
+        <v>0.011456</v>
       </c>
       <c r="C515" t="n">
         <v>0.86755</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.011762</v>
+        <v>0.011609</v>
       </c>
       <c r="C516" t="n">
         <v>0.8653419999999999</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.011794</v>
+        <v>0.01187</v>
       </c>
       <c r="C517" t="n">
         <v>0.863135</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.012107</v>
+        <v>0.011886</v>
       </c>
       <c r="C518" t="n">
         <v>0.860927</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.012257</v>
+        <v>0.012074</v>
       </c>
       <c r="C519" t="n">
         <v>0.85872</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.012259</v>
+        <v>0.012208</v>
       </c>
       <c r="C520" t="n">
         <v>0.8565120000000001</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.012797</v>
+        <v>0.012763</v>
       </c>
       <c r="C521" t="n">
         <v>0.854305</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.012851</v>
+        <v>0.012807</v>
       </c>
       <c r="C522" t="n">
         <v>0.852097</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.012987</v>
+        <v>0.012868</v>
       </c>
       <c r="C523" t="n">
         <v>0.84989</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.01301</v>
+        <v>0.012915</v>
       </c>
       <c r="C524" t="n">
         <v>0.847682</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.013045</v>
+        <v>0.013072</v>
       </c>
       <c r="C525" t="n">
         <v>0.845475</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.013281</v>
+        <v>0.013419</v>
       </c>
       <c r="C526" t="n">
         <v>0.843267</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.013694</v>
+        <v>0.013733</v>
       </c>
       <c r="C527" t="n">
         <v>0.84106</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.0137</v>
+        <v>0.013833</v>
       </c>
       <c r="C528" t="n">
         <v>0.838852</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.014059</v>
+        <v>0.013922</v>
       </c>
       <c r="C529" t="n">
         <v>0.836645</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.014762</v>
+        <v>0.01469</v>
       </c>
       <c r="C530" t="n">
         <v>0.834437</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.015268</v>
+        <v>0.01505</v>
       </c>
       <c r="C531" t="n">
         <v>0.83223</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.015494</v>
+        <v>0.015152</v>
       </c>
       <c r="C532" t="n">
         <v>0.830022</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.015618</v>
+        <v>0.015198</v>
       </c>
       <c r="C533" t="n">
         <v>0.827815</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.015712</v>
+        <v>0.015592</v>
       </c>
       <c r="C534" t="n">
         <v>0.825607</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.015714</v>
+        <v>0.015655</v>
       </c>
       <c r="C535" t="n">
         <v>0.8234</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.015719</v>
+        <v>0.015667</v>
       </c>
       <c r="C536" t="n">
         <v>0.821192</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.01583</v>
+        <v>0.015685</v>
       </c>
       <c r="C537" t="n">
         <v>0.818985</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.01589</v>
+        <v>0.015783</v>
       </c>
       <c r="C538" t="n">
         <v>0.816777</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.015995</v>
+        <v>0.015913</v>
       </c>
       <c r="C539" t="n">
         <v>0.81457</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.016037</v>
+        <v>0.016039</v>
       </c>
       <c r="C540" t="n">
         <v>0.812362</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.016066</v>
+        <v>0.016068</v>
       </c>
       <c r="C541" t="n">
         <v>0.810155</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.016173</v>
+        <v>0.016093</v>
       </c>
       <c r="C542" t="n">
         <v>0.807947</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.01674</v>
+        <v>0.016217</v>
       </c>
       <c r="C543" t="n">
         <v>0.80574</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.016756</v>
+        <v>0.016262</v>
       </c>
       <c r="C544" t="n">
         <v>0.803532</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.01685</v>
+        <v>0.016707</v>
       </c>
       <c r="C545" t="n">
         <v>0.801325</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.016949</v>
+        <v>0.016786</v>
       </c>
       <c r="C546" t="n">
         <v>0.799117</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.017346</v>
+        <v>0.017184</v>
       </c>
       <c r="C547" t="n">
         <v>0.796909</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.017483</v>
+        <v>0.017421</v>
       </c>
       <c r="C548" t="n">
         <v>0.794702</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.017684</v>
+        <v>0.017551</v>
       </c>
       <c r="C549" t="n">
         <v>0.792494</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.018411</v>
+        <v>0.017851</v>
       </c>
       <c r="C550" t="n">
         <v>0.790287</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.018473</v>
+        <v>0.018371</v>
       </c>
       <c r="C551" t="n">
         <v>0.788079</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.018503</v>
+        <v>0.018431</v>
       </c>
       <c r="C552" t="n">
         <v>0.785872</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.018611</v>
+        <v>0.01863</v>
       </c>
       <c r="C553" t="n">
         <v>0.783664</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.018749</v>
+        <v>0.018824</v>
       </c>
       <c r="C554" t="n">
         <v>0.781457</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.01901</v>
+        <v>0.018827</v>
       </c>
       <c r="C555" t="n">
         <v>0.779249</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.019022</v>
+        <v>0.019025</v>
       </c>
       <c r="C556" t="n">
         <v>0.777042</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.019322</v>
+        <v>0.019062</v>
       </c>
       <c r="C557" t="n">
         <v>0.774834</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.019641</v>
+        <v>0.019306</v>
       </c>
       <c r="C558" t="n">
         <v>0.772627</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.01968</v>
+        <v>0.019419</v>
       </c>
       <c r="C559" t="n">
         <v>0.770419</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.019696</v>
+        <v>0.01958</v>
       </c>
       <c r="C560" t="n">
         <v>0.768212</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.019838</v>
+        <v>0.019833</v>
       </c>
       <c r="C561" t="n">
         <v>0.766004</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.01984</v>
+        <v>0.019865</v>
       </c>
       <c r="C562" t="n">
         <v>0.7637969999999999</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.020056</v>
+        <v>0.01987</v>
       </c>
       <c r="C563" t="n">
         <v>0.761589</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.020568</v>
+        <v>0.020072</v>
       </c>
       <c r="C564" t="n">
         <v>0.759382</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.02065</v>
+        <v>0.02012</v>
       </c>
       <c r="C565" t="n">
         <v>0.757174</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.020788</v>
+        <v>0.020754</v>
       </c>
       <c r="C566" t="n">
         <v>0.7549670000000001</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.020836</v>
+        <v>0.020792</v>
       </c>
       <c r="C567" t="n">
         <v>0.752759</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.021467</v>
+        <v>0.021145</v>
       </c>
       <c r="C568" t="n">
         <v>0.750552</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.021726</v>
+        <v>0.021629</v>
       </c>
       <c r="C569" t="n">
         <v>0.748344</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.021778</v>
+        <v>0.021773</v>
       </c>
       <c r="C570" t="n">
         <v>0.7461370000000001</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.022623</v>
+        <v>0.022829</v>
       </c>
       <c r="C571" t="n">
         <v>0.743929</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.022842</v>
+        <v>0.023012</v>
       </c>
       <c r="C572" t="n">
         <v>0.741722</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.022956</v>
+        <v>0.023127</v>
       </c>
       <c r="C573" t="n">
         <v>0.739514</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.024057</v>
+        <v>0.023137</v>
       </c>
       <c r="C574" t="n">
         <v>0.737307</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.024188</v>
+        <v>0.02428</v>
       </c>
       <c r="C575" t="n">
         <v>0.7350989999999999</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.024308</v>
+        <v>0.024661</v>
       </c>
       <c r="C576" t="n">
         <v>0.732892</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.024592</v>
+        <v>0.024686</v>
       </c>
       <c r="C577" t="n">
         <v>0.730684</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.024654</v>
+        <v>0.024733</v>
       </c>
       <c r="C578" t="n">
         <v>0.728477</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.024926</v>
+        <v>0.025119</v>
       </c>
       <c r="C579" t="n">
         <v>0.7262690000000001</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.025045</v>
+        <v>0.025139</v>
       </c>
       <c r="C580" t="n">
         <v>0.724062</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.025211</v>
+        <v>0.025262</v>
       </c>
       <c r="C581" t="n">
         <v>0.721854</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.02553</v>
+        <v>0.025648</v>
       </c>
       <c r="C582" t="n">
         <v>0.719647</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.025842</v>
+        <v>0.025677</v>
       </c>
       <c r="C583" t="n">
         <v>0.717439</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.025936</v>
+        <v>0.026139</v>
       </c>
       <c r="C584" t="n">
         <v>0.715232</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.026144</v>
+        <v>0.026297</v>
       </c>
       <c r="C585" t="n">
         <v>0.713024</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.027492</v>
+        <v>0.026431</v>
       </c>
       <c r="C586" t="n">
         <v>0.710817</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.02779</v>
+        <v>0.026748</v>
       </c>
       <c r="C587" t="n">
         <v>0.708609</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.027998</v>
+        <v>0.026931</v>
       </c>
       <c r="C588" t="n">
         <v>0.706402</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.028042</v>
+        <v>0.02722</v>
       </c>
       <c r="C589" t="n">
         <v>0.704194</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.028108</v>
+        <v>0.027517</v>
       </c>
       <c r="C590" t="n">
         <v>0.701987</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.028532</v>
+        <v>0.027931</v>
       </c>
       <c r="C591" t="n">
         <v>0.699779</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.029069</v>
+        <v>0.027959</v>
       </c>
       <c r="C592" t="n">
         <v>0.697572</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.029198</v>
+        <v>0.028018</v>
       </c>
       <c r="C593" t="n">
         <v>0.695364</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.029366</v>
+        <v>0.028237</v>
       </c>
       <c r="C594" t="n">
         <v>0.693157</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.029384</v>
+        <v>0.028237</v>
       </c>
       <c r="C595" t="n">
         <v>0.690949</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.029874</v>
+        <v>0.028384</v>
       </c>
       <c r="C596" t="n">
         <v>0.688742</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.02999</v>
+        <v>0.028606</v>
       </c>
       <c r="C597" t="n">
         <v>0.686534</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.030007</v>
+        <v>0.028889</v>
       </c>
       <c r="C598" t="n">
         <v>0.684327</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.030052</v>
+        <v>0.029435</v>
       </c>
       <c r="C599" t="n">
         <v>0.682119</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.030101</v>
+        <v>0.029533</v>
       </c>
       <c r="C600" t="n">
         <v>0.679912</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.030264</v>
+        <v>0.02963</v>
       </c>
       <c r="C601" t="n">
         <v>0.677704</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.030329</v>
+        <v>0.029938</v>
       </c>
       <c r="C602" t="n">
         <v>0.675497</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.030334</v>
+        <v>0.030014</v>
       </c>
       <c r="C603" t="n">
         <v>0.673289</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.030349</v>
+        <v>0.030014</v>
       </c>
       <c r="C604" t="n">
         <v>0.671082</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.030866</v>
+        <v>0.030495</v>
       </c>
       <c r="C605" t="n">
         <v>0.668874</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.031102</v>
+        <v>0.030752</v>
       </c>
       <c r="C606" t="n">
         <v>0.666667</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.031178</v>
+        <v>0.030782</v>
       </c>
       <c r="C607" t="n">
         <v>0.664459</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.031505</v>
+        <v>0.031291</v>
       </c>
       <c r="C608" t="n">
         <v>0.662252</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.031576</v>
+        <v>0.031338</v>
       </c>
       <c r="C609" t="n">
         <v>0.660044</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.031911</v>
+        <v>0.031621</v>
       </c>
       <c r="C610" t="n">
         <v>0.657837</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.032521</v>
+        <v>0.032062</v>
       </c>
       <c r="C611" t="n">
         <v>0.655629</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.032631</v>
+        <v>0.032133</v>
       </c>
       <c r="C612" t="n">
         <v>0.6534219999999999</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.03296</v>
+        <v>0.03214</v>
       </c>
       <c r="C613" t="n">
         <v>0.651214</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.033306</v>
+        <v>0.032614</v>
       </c>
       <c r="C614" t="n">
         <v>0.649007</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.033461</v>
+        <v>0.032681</v>
       </c>
       <c r="C615" t="n">
         <v>0.646799</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.033506</v>
+        <v>0.032742</v>
       </c>
       <c r="C616" t="n">
         <v>0.6445920000000001</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.033977</v>
+        <v>0.033512</v>
       </c>
       <c r="C617" t="n">
         <v>0.642384</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.034058</v>
+        <v>0.033553</v>
       </c>
       <c r="C618" t="n">
         <v>0.640177</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.034761</v>
+        <v>0.033879</v>
       </c>
       <c r="C619" t="n">
         <v>0.637969</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.034826</v>
+        <v>0.033996</v>
       </c>
       <c r="C620" t="n">
         <v>0.635762</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.035429</v>
+        <v>0.034831</v>
       </c>
       <c r="C621" t="n">
         <v>0.633554</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.035769</v>
+        <v>0.034843</v>
       </c>
       <c r="C622" t="n">
         <v>0.631347</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.035945</v>
+        <v>0.035081</v>
       </c>
       <c r="C623" t="n">
         <v>0.629139</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.035949</v>
+        <v>0.035159</v>
       </c>
       <c r="C624" t="n">
         <v>0.626932</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.036172</v>
+        <v>0.035301</v>
       </c>
       <c r="C625" t="n">
         <v>0.6247239999999999</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.036471</v>
+        <v>0.035618</v>
       </c>
       <c r="C626" t="n">
         <v>0.622517</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.036569</v>
+        <v>0.035935</v>
       </c>
       <c r="C627" t="n">
         <v>0.620309</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.036575</v>
+        <v>0.036126</v>
       </c>
       <c r="C628" t="n">
         <v>0.618102</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.036834</v>
+        <v>0.036553</v>
       </c>
       <c r="C629" t="n">
         <v>0.6158940000000001</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.03721</v>
+        <v>0.036565</v>
       </c>
       <c r="C630" t="n">
         <v>0.613687</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.037261</v>
+        <v>0.036771</v>
       </c>
       <c r="C631" t="n">
         <v>0.611479</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.037564</v>
+        <v>0.037006</v>
       </c>
       <c r="C632" t="n">
         <v>0.609272</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.037868</v>
+        <v>0.037062</v>
       </c>
       <c r="C633" t="n">
         <v>0.607064</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.03797</v>
+        <v>0.037485</v>
       </c>
       <c r="C634" t="n">
         <v>0.604857</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.038091</v>
+        <v>0.037533</v>
       </c>
       <c r="C635" t="n">
         <v>0.602649</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.038122</v>
+        <v>0.037652</v>
       </c>
       <c r="C636" t="n">
         <v>0.600442</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.038558</v>
+        <v>0.037693</v>
       </c>
       <c r="C637" t="n">
         <v>0.598234</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.038837</v>
+        <v>0.037746</v>
       </c>
       <c r="C638" t="n">
         <v>0.5960259999999999</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.039063</v>
+        <v>0.038031</v>
       </c>
       <c r="C639" t="n">
         <v>0.593819</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.03927</v>
+        <v>0.038073</v>
       </c>
       <c r="C640" t="n">
         <v>0.591611</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.039336</v>
+        <v>0.038217</v>
       </c>
       <c r="C641" t="n">
         <v>0.589404</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.039622</v>
+        <v>0.0383</v>
       </c>
       <c r="C642" t="n">
         <v>0.5871960000000001</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.039664</v>
+        <v>0.038477</v>
       </c>
       <c r="C643" t="n">
         <v>0.584989</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.040071</v>
+        <v>0.039129</v>
       </c>
       <c r="C644" t="n">
         <v>0.582781</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.040533</v>
+        <v>0.039294</v>
       </c>
       <c r="C645" t="n">
         <v>0.580574</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.040602</v>
+        <v>0.039305</v>
       </c>
       <c r="C646" t="n">
         <v>0.578366</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.040836</v>
+        <v>0.039587</v>
       </c>
       <c r="C647" t="n">
         <v>0.576159</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.041045</v>
+        <v>0.039739</v>
       </c>
       <c r="C648" t="n">
         <v>0.573951</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.041087</v>
+        <v>0.039831</v>
       </c>
       <c r="C649" t="n">
         <v>0.571744</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.041097</v>
+        <v>0.040232</v>
       </c>
       <c r="C650" t="n">
         <v>0.569536</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.041174</v>
+        <v>0.040352</v>
       </c>
       <c r="C651" t="n">
         <v>0.567329</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.042121</v>
+        <v>0.040387</v>
       </c>
       <c r="C652" t="n">
         <v>0.565121</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.042124</v>
+        <v>0.040715</v>
       </c>
       <c r="C653" t="n">
         <v>0.562914</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.042135</v>
+        <v>0.040998</v>
       </c>
       <c r="C654" t="n">
         <v>0.560706</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.042335</v>
+        <v>0.041161</v>
       </c>
       <c r="C655" t="n">
         <v>0.558499</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.042834</v>
+        <v>0.041806</v>
       </c>
       <c r="C656" t="n">
         <v>0.556291</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.043603</v>
+        <v>0.042036</v>
       </c>
       <c r="C657" t="n">
         <v>0.554084</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.043892</v>
+        <v>0.042238</v>
       </c>
       <c r="C658" t="n">
         <v>0.551876</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.043913</v>
+        <v>0.042335</v>
       </c>
       <c r="C659" t="n">
         <v>0.549669</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.044188</v>
+        <v>0.042679</v>
       </c>
       <c r="C660" t="n">
         <v>0.547461</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.044236</v>
+        <v>0.042684</v>
       </c>
       <c r="C661" t="n">
         <v>0.545254</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.044332</v>
+        <v>0.04271</v>
       </c>
       <c r="C662" t="n">
         <v>0.543046</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.044334</v>
+        <v>0.042816</v>
       </c>
       <c r="C663" t="n">
         <v>0.540839</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.045101</v>
+        <v>0.043264</v>
       </c>
       <c r="C664" t="n">
         <v>0.538631</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.045121</v>
+        <v>0.043568</v>
       </c>
       <c r="C665" t="n">
         <v>0.536424</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.04519</v>
+        <v>0.043751</v>
       </c>
       <c r="C666" t="n">
         <v>0.534216</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.045236</v>
+        <v>0.044079</v>
       </c>
       <c r="C667" t="n">
         <v>0.532009</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.045424</v>
+        <v>0.044107</v>
       </c>
       <c r="C668" t="n">
         <v>0.529801</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.045669</v>
+        <v>0.044746</v>
       </c>
       <c r="C669" t="n">
         <v>0.527594</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.045739</v>
+        <v>0.044881</v>
       </c>
       <c r="C670" t="n">
         <v>0.525386</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.045946</v>
+        <v>0.045163</v>
       </c>
       <c r="C671" t="n">
         <v>0.5231789999999999</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.046613</v>
+        <v>0.045305</v>
       </c>
       <c r="C672" t="n">
         <v>0.520971</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.046744</v>
+        <v>0.046818</v>
       </c>
       <c r="C673" t="n">
         <v>0.518764</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.047391</v>
+        <v>0.047266</v>
       </c>
       <c r="C674" t="n">
         <v>0.516556</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.047476</v>
+        <v>0.047561</v>
       </c>
       <c r="C675" t="n">
         <v>0.5143489999999999</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.048257</v>
+        <v>0.048013</v>
       </c>
       <c r="C676" t="n">
         <v>0.512141</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.048968</v>
+        <v>0.0486</v>
       </c>
       <c r="C677" t="n">
         <v>0.509934</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.049272</v>
+        <v>0.048833</v>
       </c>
       <c r="C678" t="n">
         <v>0.507726</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.049435</v>
+        <v>0.04886</v>
       </c>
       <c r="C679" t="n">
         <v>0.5055190000000001</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.049466</v>
+        <v>0.049067</v>
       </c>
       <c r="C680" t="n">
         <v>0.503311</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.049708</v>
+        <v>0.049204</v>
       </c>
       <c r="C681" t="n">
         <v>0.501104</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.04972</v>
+        <v>0.049505</v>
       </c>
       <c r="C682" t="n">
         <v>0.498896</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.05032</v>
+        <v>0.049639</v>
       </c>
       <c r="C683" t="n">
         <v>0.496689</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.050505</v>
+        <v>0.050096</v>
       </c>
       <c r="C684" t="n">
         <v>0.494481</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.051549</v>
+        <v>0.050492</v>
       </c>
       <c r="C685" t="n">
         <v>0.492274</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.05176</v>
+        <v>0.050526</v>
       </c>
       <c r="C686" t="n">
         <v>0.490066</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.052841</v>
+        <v>0.051557</v>
       </c>
       <c r="C687" t="n">
         <v>0.487859</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.05288</v>
+        <v>0.051627</v>
       </c>
       <c r="C688" t="n">
         <v>0.485651</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.052886</v>
+        <v>0.052538</v>
       </c>
       <c r="C689" t="n">
         <v>0.483444</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.052938</v>
+        <v>0.05308</v>
       </c>
       <c r="C690" t="n">
         <v>0.481236</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.05331</v>
+        <v>0.053217</v>
       </c>
       <c r="C691" t="n">
         <v>0.479029</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.053734</v>
+        <v>0.053375</v>
       </c>
       <c r="C692" t="n">
         <v>0.476821</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.054402</v>
+        <v>0.053593</v>
       </c>
       <c r="C693" t="n">
         <v>0.474614</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.054569</v>
+        <v>0.05362</v>
       </c>
       <c r="C694" t="n">
         <v>0.472406</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.054769</v>
+        <v>0.054666</v>
       </c>
       <c r="C695" t="n">
         <v>0.470199</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.055034</v>
+        <v>0.054871</v>
       </c>
       <c r="C696" t="n">
         <v>0.467991</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.056156</v>
+        <v>0.055241</v>
       </c>
       <c r="C697" t="n">
         <v>0.465784</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.05621</v>
+        <v>0.055289</v>
       </c>
       <c r="C698" t="n">
         <v>0.463576</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.056869</v>
+        <v>0.055782</v>
       </c>
       <c r="C699" t="n">
         <v>0.461369</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.05697</v>
+        <v>0.056428</v>
       </c>
       <c r="C700" t="n">
         <v>0.459161</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.057173</v>
+        <v>0.056868</v>
       </c>
       <c r="C701" t="n">
         <v>0.456954</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.059445</v>
+        <v>0.057239</v>
       </c>
       <c r="C702" t="n">
         <v>0.454746</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.059701</v>
+        <v>0.057427</v>
       </c>
       <c r="C703" t="n">
         <v>0.452539</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.060067</v>
+        <v>0.057667</v>
       </c>
       <c r="C704" t="n">
         <v>0.450331</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.060115</v>
+        <v>0.059213</v>
       </c>
       <c r="C705" t="n">
         <v>0.448124</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.060406</v>
+        <v>0.059446</v>
       </c>
       <c r="C706" t="n">
         <v>0.445916</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.060776</v>
+        <v>0.059935</v>
       </c>
       <c r="C707" t="n">
         <v>0.443709</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.060955</v>
+        <v>0.060226</v>
       </c>
       <c r="C708" t="n">
         <v>0.441501</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.061256</v>
+        <v>0.060659</v>
       </c>
       <c r="C709" t="n">
         <v>0.439294</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.062174</v>
+        <v>0.060668</v>
       </c>
       <c r="C710" t="n">
         <v>0.437086</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.062277</v>
+        <v>0.060909</v>
       </c>
       <c r="C711" t="n">
         <v>0.434879</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.062447</v>
+        <v>0.060942</v>
       </c>
       <c r="C712" t="n">
         <v>0.432671</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.062663</v>
+        <v>0.061118</v>
       </c>
       <c r="C713" t="n">
         <v>0.430464</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.063208</v>
+        <v>0.061564</v>
       </c>
       <c r="C714" t="n">
         <v>0.428256</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.063245</v>
+        <v>0.062491</v>
       </c>
       <c r="C715" t="n">
         <v>0.426049</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.063481</v>
+        <v>0.062502</v>
       </c>
       <c r="C716" t="n">
         <v>0.423841</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.063656</v>
+        <v>0.06349200000000001</v>
       </c>
       <c r="C717" t="n">
         <v>0.421634</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.063939</v>
+        <v>0.063793</v>
       </c>
       <c r="C718" t="n">
         <v>0.419426</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.06410299999999999</v>
+        <v>0.06407400000000001</v>
       </c>
       <c r="C719" t="n">
         <v>0.417219</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.064327</v>
+        <v>0.064083</v>
       </c>
       <c r="C720" t="n">
         <v>0.415011</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.064913</v>
+        <v>0.064193</v>
       </c>
       <c r="C721" t="n">
         <v>0.412804</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.06506000000000001</v>
+        <v>0.064263</v>
       </c>
       <c r="C722" t="n">
         <v>0.410596</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.06518500000000001</v>
+        <v>0.064683</v>
       </c>
       <c r="C723" t="n">
         <v>0.408389</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.06619700000000001</v>
+        <v>0.064708</v>
       </c>
       <c r="C724" t="n">
         <v>0.406181</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.06743300000000001</v>
+        <v>0.065014</v>
       </c>
       <c r="C725" t="n">
         <v>0.403974</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.067647</v>
+        <v>0.06503100000000001</v>
       </c>
       <c r="C726" t="n">
         <v>0.401766</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.067735</v>
+        <v>0.065346</v>
       </c>
       <c r="C727" t="n">
         <v>0.399558</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.067963</v>
+        <v>0.06557499999999999</v>
       </c>
       <c r="C728" t="n">
         <v>0.397351</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.068125</v>
+        <v>0.06566</v>
       </c>
       <c r="C729" t="n">
         <v>0.395143</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.068352</v>
+        <v>0.06707299999999999</v>
       </c>
       <c r="C730" t="n">
         <v>0.392936</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.068423</v>
+        <v>0.067288</v>
       </c>
       <c r="C731" t="n">
         <v>0.390728</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.06929200000000001</v>
+        <v>0.067457</v>
       </c>
       <c r="C732" t="n">
         <v>0.388521</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.069494</v>
+        <v>0.06748800000000001</v>
       </c>
       <c r="C733" t="n">
         <v>0.386313</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.069505</v>
+        <v>0.06770900000000001</v>
       </c>
       <c r="C734" t="n">
         <v>0.384106</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.06967</v>
+        <v>0.06825100000000001</v>
       </c>
       <c r="C735" t="n">
         <v>0.381898</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.069697</v>
+        <v>0.068319</v>
       </c>
       <c r="C736" t="n">
         <v>0.379691</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.069857</v>
+        <v>0.068482</v>
       </c>
       <c r="C737" t="n">
         <v>0.377483</v>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.070039</v>
+        <v>0.068897</v>
       </c>
       <c r="C738" t="n">
         <v>0.375276</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.070299</v>
+        <v>0.06959700000000001</v>
       </c>
       <c r="C739" t="n">
         <v>0.373068</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.070324</v>
+        <v>0.06983200000000001</v>
       </c>
       <c r="C740" t="n">
         <v>0.370861</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.071003</v>
+        <v>0.06997200000000001</v>
       </c>
       <c r="C741" t="n">
         <v>0.368653</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.07116599999999999</v>
+        <v>0.070104</v>
       </c>
       <c r="C742" t="n">
         <v>0.366446</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.071436</v>
+        <v>0.07015299999999999</v>
       </c>
       <c r="C743" t="n">
         <v>0.364238</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.071475</v>
+        <v>0.07027</v>
       </c>
       <c r="C744" t="n">
         <v>0.362031</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.071592</v>
+        <v>0.07121</v>
       </c>
       <c r="C745" t="n">
         <v>0.359823</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.071677</v>
+        <v>0.07148</v>
       </c>
       <c r="C746" t="n">
         <v>0.357616</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.072135</v>
+        <v>0.07192900000000001</v>
       </c>
       <c r="C747" t="n">
         <v>0.355408</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.072495</v>
+        <v>0.072209</v>
       </c>
       <c r="C748" t="n">
         <v>0.353201</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.072976</v>
+        <v>0.07222000000000001</v>
       </c>
       <c r="C749" t="n">
         <v>0.350993</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.073297</v>
+        <v>0.072326</v>
       </c>
       <c r="C750" t="n">
         <v>0.348786</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.07363500000000001</v>
+        <v>0.072334</v>
       </c>
       <c r="C751" t="n">
         <v>0.346578</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.074832</v>
+        <v>0.072629</v>
       </c>
       <c r="C752" t="n">
         <v>0.344371</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.074849</v>
+        <v>0.073333</v>
       </c>
       <c r="C753" t="n">
         <v>0.342163</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.075041</v>
+        <v>0.073546</v>
       </c>
       <c r="C754" t="n">
         <v>0.339956</v>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.075097</v>
+        <v>0.073657</v>
       </c>
       <c r="C755" t="n">
         <v>0.337748</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.07513400000000001</v>
+        <v>0.073808</v>
       </c>
       <c r="C756" t="n">
         <v>0.335541</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.076284</v>
+        <v>0.074457</v>
       </c>
       <c r="C757" t="n">
         <v>0.333333</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.07717499999999999</v>
+        <v>0.074841</v>
       </c>
       <c r="C758" t="n">
         <v>0.331126</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.077227</v>
+        <v>0.074986</v>
       </c>
       <c r="C759" t="n">
         <v>0.328918</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.077417</v>
+        <v>0.075199</v>
       </c>
       <c r="C760" t="n">
         <v>0.326711</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.07825500000000001</v>
+        <v>0.07555099999999999</v>
       </c>
       <c r="C761" t="n">
         <v>0.324503</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.07835499999999999</v>
+        <v>0.075748</v>
       </c>
       <c r="C762" t="n">
         <v>0.322296</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.07872800000000001</v>
+        <v>0.07605000000000001</v>
       </c>
       <c r="C763" t="n">
         <v>0.320088</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.078846</v>
+        <v>0.076889</v>
       </c>
       <c r="C764" t="n">
         <v>0.317881</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.078985</v>
+        <v>0.078237</v>
       </c>
       <c r="C765" t="n">
         <v>0.315673</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.079128</v>
+        <v>0.078781</v>
       </c>
       <c r="C766" t="n">
         <v>0.313466</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.079625</v>
+        <v>0.079085</v>
       </c>
       <c r="C767" t="n">
         <v>0.311258</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.080016</v>
+        <v>0.079746</v>
       </c>
       <c r="C768" t="n">
         <v>0.309051</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.080982</v>
+        <v>0.079816</v>
       </c>
       <c r="C769" t="n">
         <v>0.306843</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.08172599999999999</v>
+        <v>0.079848</v>
       </c>
       <c r="C770" t="n">
         <v>0.304636</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.082027</v>
+        <v>0.08075599999999999</v>
       </c>
       <c r="C771" t="n">
         <v>0.302428</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.082056</v>
+        <v>0.081105</v>
       </c>
       <c r="C772" t="n">
         <v>0.300221</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.08275399999999999</v>
+        <v>0.081569</v>
       </c>
       <c r="C773" t="n">
         <v>0.298013</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.08276799999999999</v>
+        <v>0.081606</v>
       </c>
       <c r="C774" t="n">
         <v>0.295806</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.084367</v>
+        <v>0.08219</v>
       </c>
       <c r="C775" t="n">
         <v>0.293598</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.08450299999999999</v>
+        <v>0.082258</v>
       </c>
       <c r="C776" t="n">
         <v>0.291391</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.084575</v>
+        <v>0.083331</v>
       </c>
       <c r="C777" t="n">
         <v>0.289183</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.084855</v>
+        <v>0.083847</v>
       </c>
       <c r="C778" t="n">
         <v>0.286976</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.08545899999999999</v>
+        <v>0.084328</v>
       </c>
       <c r="C779" t="n">
         <v>0.284768</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.086294</v>
+        <v>0.08505500000000001</v>
       </c>
       <c r="C780" t="n">
         <v>0.282561</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.08637400000000001</v>
+        <v>0.085384</v>
       </c>
       <c r="C781" t="n">
         <v>0.280353</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.086394</v>
+        <v>0.085646</v>
       </c>
       <c r="C782" t="n">
         <v>0.278146</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.086994</v>
+        <v>0.085956</v>
       </c>
       <c r="C783" t="n">
         <v>0.275938</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.08901299999999999</v>
+        <v>0.086109</v>
       </c>
       <c r="C784" t="n">
         <v>0.273731</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.08958099999999999</v>
+        <v>0.086157</v>
       </c>
       <c r="C785" t="n">
         <v>0.271523</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.089666</v>
+        <v>0.086741</v>
       </c>
       <c r="C786" t="n">
         <v>0.269316</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.090169</v>
+        <v>0.08683100000000001</v>
       </c>
       <c r="C787" t="n">
         <v>0.267108</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.09128799999999999</v>
+        <v>0.088212</v>
       </c>
       <c r="C788" t="n">
         <v>0.264901</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.09148299999999999</v>
+        <v>0.08834699999999999</v>
       </c>
       <c r="C789" t="n">
         <v>0.262693</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>0.092144</v>
+        <v>0.08877599999999999</v>
       </c>
       <c r="C790" t="n">
         <v>0.260486</v>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>0.092414</v>
+        <v>0.088826</v>
       </c>
       <c r="C791" t="n">
         <v>0.258278</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>0.092475</v>
+        <v>0.090172</v>
       </c>
       <c r="C792" t="n">
         <v>0.256071</v>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>0.093226</v>
+        <v>0.090271</v>
       </c>
       <c r="C793" t="n">
         <v>0.253863</v>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>0.093319</v>
+        <v>0.090702</v>
       </c>
       <c r="C794" t="n">
         <v>0.251656</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.093444</v>
+        <v>0.0919</v>
       </c>
       <c r="C795" t="n">
         <v>0.249448</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.094275</v>
+        <v>0.092486</v>
       </c>
       <c r="C796" t="n">
         <v>0.247241</v>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>0.094308</v>
+        <v>0.092556</v>
       </c>
       <c r="C797" t="n">
         <v>0.245033</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>0.094374</v>
+        <v>0.093601</v>
       </c>
       <c r="C798" t="n">
         <v>0.242826</v>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>0.09514599999999999</v>
+        <v>0.094264</v>
       </c>
       <c r="C799" t="n">
         <v>0.240618</v>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>0.095454</v>
+        <v>0.09496400000000001</v>
       </c>
       <c r="C800" t="n">
         <v>0.238411</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="B801" t="n">
-        <v>0.09629</v>
+        <v>0.095235</v>
       </c>
       <c r="C801" t="n">
         <v>0.236203</v>
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="B802" t="n">
-        <v>0.096786</v>
+        <v>0.09618699999999999</v>
       </c>
       <c r="C802" t="n">
         <v>0.233996</v>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="B803" t="n">
-        <v>0.097355</v>
+        <v>0.097113</v>
       </c>
       <c r="C803" t="n">
         <v>0.231788</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>0.09861300000000001</v>
+        <v>0.097233</v>
       </c>
       <c r="C804" t="n">
         <v>0.229581</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="B805" t="n">
-        <v>0.09864000000000001</v>
+        <v>0.097951</v>
       </c>
       <c r="C805" t="n">
         <v>0.227373</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="B806" t="n">
-        <v>0.098653</v>
+        <v>0.099319</v>
       </c>
       <c r="C806" t="n">
         <v>0.225166</v>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="B807" t="n">
-        <v>0.100076</v>
+        <v>0.099511</v>
       </c>
       <c r="C807" t="n">
         <v>0.222958</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>0.1011</v>
+        <v>0.099927</v>
       </c>
       <c r="C808" t="n">
         <v>0.220751</v>
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>0.103473</v>
+        <v>0.100026</v>
       </c>
       <c r="C809" t="n">
         <v>0.218543</v>
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>0.105587</v>
+        <v>0.100592</v>
       </c>
       <c r="C810" t="n">
         <v>0.216336</v>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0.105689</v>
+        <v>0.101767</v>
       </c>
       <c r="C811" t="n">
         <v>0.214128</v>
@@ -10970,7 +10970,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>0.106297</v>
+        <v>0.1019</v>
       </c>
       <c r="C812" t="n">
         <v>0.211921</v>
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.107254</v>
+        <v>0.102788</v>
       </c>
       <c r="C813" t="n">
         <v>0.209713</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>0.107466</v>
+        <v>0.106009</v>
       </c>
       <c r="C814" t="n">
         <v>0.207506</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>0.108627</v>
+        <v>0.107031</v>
       </c>
       <c r="C815" t="n">
         <v>0.205298</v>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>0.108998</v>
+        <v>0.108222</v>
       </c>
       <c r="C816" t="n">
         <v>0.203091</v>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>0.111546</v>
+        <v>0.109455</v>
       </c>
       <c r="C817" t="n">
         <v>0.200883</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>0.111612</v>
+        <v>0.110851</v>
       </c>
       <c r="C818" t="n">
         <v>0.198675</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="B819" t="n">
-        <v>0.113035</v>
+        <v>0.111345</v>
       </c>
       <c r="C819" t="n">
         <v>0.196468</v>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="B820" t="n">
-        <v>0.114834</v>
+        <v>0.112739</v>
       </c>
       <c r="C820" t="n">
         <v>0.19426</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>0.115102</v>
+        <v>0.113011</v>
       </c>
       <c r="C821" t="n">
         <v>0.192053</v>
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="B822" t="n">
-        <v>0.115907</v>
+        <v>0.113265</v>
       </c>
       <c r="C822" t="n">
         <v>0.189845</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>0.117953</v>
+        <v>0.115701</v>
       </c>
       <c r="C823" t="n">
         <v>0.187638</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>0.11807</v>
+        <v>0.116624</v>
       </c>
       <c r="C824" t="n">
         <v>0.18543</v>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>0.118658</v>
+        <v>0.117001</v>
       </c>
       <c r="C825" t="n">
         <v>0.183223</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.120241</v>
+        <v>0.11729</v>
       </c>
       <c r="C826" t="n">
         <v>0.181015</v>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>0.121614</v>
+        <v>0.119936</v>
       </c>
       <c r="C827" t="n">
         <v>0.178808</v>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="B828" t="n">
-        <v>0.121629</v>
+        <v>0.120496</v>
       </c>
       <c r="C828" t="n">
         <v>0.1766</v>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>0.122872</v>
+        <v>0.122149</v>
       </c>
       <c r="C829" t="n">
         <v>0.174393</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>0.123726</v>
+        <v>0.122371</v>
       </c>
       <c r="C830" t="n">
         <v>0.172185</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>0.123912</v>
+        <v>0.12245</v>
       </c>
       <c r="C831" t="n">
         <v>0.169978</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B832" t="n">
-        <v>0.1252</v>
+        <v>0.123873</v>
       </c>
       <c r="C832" t="n">
         <v>0.16777</v>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>0.125834</v>
+        <v>0.124617</v>
       </c>
       <c r="C833" t="n">
         <v>0.165563</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>0.126517</v>
+        <v>0.12475</v>
       </c>
       <c r="C834" t="n">
         <v>0.163355</v>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="B835" t="n">
-        <v>0.127526</v>
+        <v>0.125711</v>
       </c>
       <c r="C835" t="n">
         <v>0.161148</v>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>0.127876</v>
+        <v>0.126436</v>
       </c>
       <c r="C836" t="n">
         <v>0.15894</v>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>0.128244</v>
+        <v>0.127613</v>
       </c>
       <c r="C837" t="n">
         <v>0.156733</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>0.132756</v>
+        <v>0.127752</v>
       </c>
       <c r="C838" t="n">
         <v>0.154525</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.132948</v>
+        <v>0.128601</v>
       </c>
       <c r="C839" t="n">
         <v>0.152318</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>0.133145</v>
+        <v>0.128754</v>
       </c>
       <c r="C840" t="n">
         <v>0.15011</v>
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.133656</v>
+        <v>0.129246</v>
       </c>
       <c r="C841" t="n">
         <v>0.147903</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.1343</v>
+        <v>0.132716</v>
       </c>
       <c r="C842" t="n">
         <v>0.145695</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="B843" t="n">
-        <v>0.136586</v>
+        <v>0.133321</v>
       </c>
       <c r="C843" t="n">
         <v>0.143488</v>
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>0.137129</v>
+        <v>0.133331</v>
       </c>
       <c r="C844" t="n">
         <v>0.14128</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.138508</v>
+        <v>0.134727</v>
       </c>
       <c r="C845" t="n">
         <v>0.139073</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>0.141194</v>
+        <v>0.134783</v>
       </c>
       <c r="C846" t="n">
         <v>0.136865</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>0.144415</v>
+        <v>0.135526</v>
       </c>
       <c r="C847" t="n">
         <v>0.134658</v>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>0.144932</v>
+        <v>0.136342</v>
       </c>
       <c r="C848" t="n">
         <v>0.13245</v>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>0.145252</v>
+        <v>0.138644</v>
       </c>
       <c r="C849" t="n">
         <v>0.130243</v>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>0.147664</v>
+        <v>0.139208</v>
       </c>
       <c r="C850" t="n">
         <v>0.128035</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>0.148255</v>
+        <v>0.143301</v>
       </c>
       <c r="C851" t="n">
         <v>0.125828</v>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.149594</v>
+        <v>0.14364</v>
       </c>
       <c r="C852" t="n">
         <v>0.12362</v>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>0.150896</v>
+        <v>0.144938</v>
       </c>
       <c r="C853" t="n">
         <v>0.121413</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.150969</v>
+        <v>0.148018</v>
       </c>
       <c r="C854" t="n">
         <v>0.119205</v>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>0.152865</v>
+        <v>0.149791</v>
       </c>
       <c r="C855" t="n">
         <v>0.116998</v>
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>0.153746</v>
+        <v>0.150906</v>
       </c>
       <c r="C856" t="n">
         <v>0.11479</v>
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>0.154138</v>
+        <v>0.153213</v>
       </c>
       <c r="C857" t="n">
         <v>0.112583</v>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>0.156635</v>
+        <v>0.155049</v>
       </c>
       <c r="C858" t="n">
         <v>0.110375</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.157229</v>
+        <v>0.157527</v>
       </c>
       <c r="C859" t="n">
         <v>0.108168</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>0.162685</v>
+        <v>0.158509</v>
       </c>
       <c r="C860" t="n">
         <v>0.10596</v>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="B861" t="n">
-        <v>0.163087</v>
+        <v>0.163156</v>
       </c>
       <c r="C861" t="n">
         <v>0.103753</v>
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="B862" t="n">
-        <v>0.168563</v>
+        <v>0.163622</v>
       </c>
       <c r="C862" t="n">
         <v>0.101545</v>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="B863" t="n">
-        <v>0.169944</v>
+        <v>0.164656</v>
       </c>
       <c r="C863" t="n">
         <v>0.099338</v>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="B864" t="n">
-        <v>0.171642</v>
+        <v>0.167691</v>
       </c>
       <c r="C864" t="n">
         <v>0.09712999999999999</v>
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="B865" t="n">
-        <v>0.171642</v>
+        <v>0.168478</v>
       </c>
       <c r="C865" t="n">
         <v>0.09492299999999999</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B866" t="n">
-        <v>0.171642</v>
+        <v>0.169374</v>
       </c>
       <c r="C866" t="n">
         <v>0.09271500000000001</v>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>0.172747</v>
+        <v>0.169374</v>
       </c>
       <c r="C867" t="n">
         <v>0.09050800000000001</v>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="B868" t="n">
-        <v>0.177674</v>
+        <v>0.169374</v>
       </c>
       <c r="C868" t="n">
         <v>0.0883</v>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="B869" t="n">
-        <v>0.181466</v>
+        <v>0.169918</v>
       </c>
       <c r="C869" t="n">
         <v>0.086093</v>
@@ -11724,7 +11724,7 @@
         </is>
       </c>
       <c r="B870" t="n">
-        <v>0.181841</v>
+        <v>0.171184</v>
       </c>
       <c r="C870" t="n">
         <v>0.083885</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="B871" t="n">
-        <v>0.183769</v>
+        <v>0.174478</v>
       </c>
       <c r="C871" t="n">
         <v>0.081678</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>0.184006</v>
+        <v>0.176903</v>
       </c>
       <c r="C872" t="n">
         <v>0.07947</v>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>0.185126</v>
+        <v>0.180769</v>
       </c>
       <c r="C873" t="n">
         <v>0.077263</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>0.185238</v>
+        <v>0.183293</v>
       </c>
       <c r="C874" t="n">
         <v>0.075055</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>0.189366</v>
+        <v>0.184943</v>
       </c>
       <c r="C875" t="n">
         <v>0.072848</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="B876" t="n">
-        <v>0.19419</v>
+        <v>0.18934</v>
       </c>
       <c r="C876" t="n">
         <v>0.07063999999999999</v>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="B877" t="n">
-        <v>0.194228</v>
+        <v>0.196198</v>
       </c>
       <c r="C877" t="n">
         <v>0.06843299999999999</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="B878" t="n">
-        <v>0.196957</v>
+        <v>0.198464</v>
       </c>
       <c r="C878" t="n">
         <v>0.06622500000000001</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>0.203954</v>
+        <v>0.199678</v>
       </c>
       <c r="C879" t="n">
         <v>0.06401800000000001</v>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>0.211249</v>
+        <v>0.211655</v>
       </c>
       <c r="C880" t="n">
         <v>0.06181</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B881" t="n">
-        <v>0.21856</v>
+        <v>0.212513</v>
       </c>
       <c r="C881" t="n">
         <v>0.059603</v>
@@ -11880,7 +11880,7 @@
         </is>
       </c>
       <c r="B882" t="n">
-        <v>0.220686</v>
+        <v>0.218092</v>
       </c>
       <c r="C882" t="n">
         <v>0.057395</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="B883" t="n">
-        <v>0.220853</v>
+        <v>0.218454</v>
       </c>
       <c r="C883" t="n">
         <v>0.055188</v>
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>0.221921</v>
+        <v>0.220225</v>
       </c>
       <c r="C884" t="n">
         <v>0.05298</v>
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>0.224118</v>
+        <v>0.22026</v>
       </c>
       <c r="C885" t="n">
         <v>0.050773</v>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="B886" t="n">
-        <v>0.227008</v>
+        <v>0.222214</v>
       </c>
       <c r="C886" t="n">
         <v>0.048565</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>0.245408</v>
+        <v>0.224456</v>
       </c>
       <c r="C887" t="n">
         <v>0.046358</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="B888" t="n">
-        <v>0.261297</v>
+        <v>0.25728</v>
       </c>
       <c r="C888" t="n">
         <v>0.04415</v>
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="B889" t="n">
-        <v>0.269983</v>
+        <v>0.262101</v>
       </c>
       <c r="C889" t="n">
         <v>0.041943</v>
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>0.272346</v>
+        <v>0.273501</v>
       </c>
       <c r="C890" t="n">
         <v>0.039735</v>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>0.279901</v>
+        <v>0.277274</v>
       </c>
       <c r="C891" t="n">
         <v>0.037528</v>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="B892" t="n">
-        <v>0.309101</v>
+        <v>0.308065</v>
       </c>
       <c r="C892" t="n">
         <v>0.03532</v>
@@ -12023,7 +12023,7 @@
         </is>
       </c>
       <c r="B893" t="n">
-        <v>0.309286</v>
+        <v>0.308375</v>
       </c>
       <c r="C893" t="n">
         <v>0.033113</v>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>0.333689</v>
+        <v>0.314041</v>
       </c>
       <c r="C894" t="n">
         <v>0.030905</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>0.343426</v>
+        <v>0.340947</v>
       </c>
       <c r="C895" t="n">
         <v>0.028698</v>
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>0.374591</v>
+        <v>0.362405</v>
       </c>
       <c r="C896" t="n">
         <v>0.02649</v>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="B897" t="n">
-        <v>0.388884</v>
+        <v>0.364905</v>
       </c>
       <c r="C897" t="n">
         <v>0.024283</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="B898" t="n">
-        <v>0.395558</v>
+        <v>0.371448</v>
       </c>
       <c r="C898" t="n">
         <v>0.022075</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>0.420689</v>
+        <v>0.384788</v>
       </c>
       <c r="C899" t="n">
         <v>0.019868</v>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="B900" t="n">
-        <v>0.430412</v>
+        <v>0.399614</v>
       </c>
       <c r="C900" t="n">
         <v>0.01766</v>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="B901" t="n">
-        <v>0.535328</v>
+        <v>0.530528</v>
       </c>
       <c r="C901" t="n">
         <v>0.015453</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="B902" t="n">
-        <v>0.548977</v>
+        <v>0.551198</v>
       </c>
       <c r="C902" t="n">
         <v>0.013245</v>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>0.674305</v>
+        <v>0.678392</v>
       </c>
       <c r="C903" t="n">
         <v>0.011038</v>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="B904" t="n">
-        <v>0.697815</v>
+        <v>0.700649</v>
       </c>
       <c r="C904" t="n">
         <v>0.008829999999999999</v>
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="B905" t="n">
-        <v>1.055045</v>
+        <v>1.002024</v>
       </c>
       <c r="C905" t="n">
         <v>0.006623</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>1.109808</v>
+        <v>1.058084</v>
       </c>
       <c r="C906" t="n">
         <v>0.004415</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>1.330462</v>
+        <v>1.351286</v>
       </c>
       <c r="C907" t="n">
         <v>0.002208</v>

--- a/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-1/tail_exceedance_plot_data.xlsx
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.000111</v>
+        <v>0.000112</v>
       </c>
       <c r="C433" t="n">
         <v>0.9976739999999999</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.000428</v>
+        <v>0.000429</v>
       </c>
       <c r="C434" t="n">
         <v>0.995349</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.001</v>
+        <v>0.000998</v>
       </c>
       <c r="C437" t="n">
         <v>0.988372</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.001069</v>
+        <v>0.00107</v>
       </c>
       <c r="C438" t="n">
         <v>0.986047</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.001653</v>
+        <v>0.001652</v>
       </c>
       <c r="C439" t="n">
         <v>0.983721</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.002016</v>
+        <v>0.002019</v>
       </c>
       <c r="C441" t="n">
         <v>0.97907</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.002407</v>
+        <v>0.002405</v>
       </c>
       <c r="C442" t="n">
         <v>0.9767439999999999</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.002565</v>
+        <v>0.002555</v>
       </c>
       <c r="C443" t="n">
         <v>0.974419</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.00275</v>
+        <v>0.002753</v>
       </c>
       <c r="C444" t="n">
         <v>0.972093</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.002843</v>
+        <v>0.002848</v>
       </c>
       <c r="C445" t="n">
         <v>0.969767</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.003017</v>
+        <v>0.003023</v>
       </c>
       <c r="C446" t="n">
         <v>0.967442</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.003097</v>
+        <v>0.0031</v>
       </c>
       <c r="C447" t="n">
         <v>0.965116</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.003499</v>
+        <v>0.003492</v>
       </c>
       <c r="C448" t="n">
         <v>0.962791</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.003887</v>
+        <v>0.003879</v>
       </c>
       <c r="C449" t="n">
         <v>0.960465</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.00396</v>
+        <v>0.003958</v>
       </c>
       <c r="C450" t="n">
         <v>0.95814</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.004235</v>
+        <v>0.004238</v>
       </c>
       <c r="C451" t="n">
         <v>0.9558140000000001</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.004346</v>
+        <v>0.004348</v>
       </c>
       <c r="C452" t="n">
         <v>0.953488</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.00453</v>
+        <v>0.004536</v>
       </c>
       <c r="C453" t="n">
         <v>0.951163</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.004564</v>
+        <v>0.004563</v>
       </c>
       <c r="C454" t="n">
         <v>0.948837</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.004601</v>
+        <v>0.004606</v>
       </c>
       <c r="C455" t="n">
         <v>0.946512</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.004656</v>
+        <v>0.004661</v>
       </c>
       <c r="C456" t="n">
         <v>0.944186</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.004783</v>
+        <v>0.004771</v>
       </c>
       <c r="C457" t="n">
         <v>0.94186</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.004827</v>
+        <v>0.004816</v>
       </c>
       <c r="C458" t="n">
         <v>0.939535</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.004885</v>
+        <v>0.00489</v>
       </c>
       <c r="C459" t="n">
         <v>0.937209</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.004983</v>
+        <v>0.004974</v>
       </c>
       <c r="C460" t="n">
         <v>0.934884</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.004988</v>
+        <v>0.004983</v>
       </c>
       <c r="C461" t="n">
         <v>0.932558</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.005324</v>
+        <v>0.005332</v>
       </c>
       <c r="C463" t="n">
         <v>0.927907</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.005623</v>
+        <v>0.005633</v>
       </c>
       <c r="C464" t="n">
         <v>0.925581</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.005696</v>
+        <v>0.0057</v>
       </c>
       <c r="C465" t="n">
         <v>0.923256</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.005752</v>
+        <v>0.005753</v>
       </c>
       <c r="C466" t="n">
         <v>0.92093</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.005878</v>
+        <v>0.005884</v>
       </c>
       <c r="C467" t="n">
         <v>0.918605</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.007399</v>
+        <v>0.00739</v>
       </c>
       <c r="C468" t="n">
         <v>0.916279</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.007736</v>
+        <v>0.007738</v>
       </c>
       <c r="C469" t="n">
         <v>0.913953</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.008163</v>
+        <v>0.008160000000000001</v>
       </c>
       <c r="C470" t="n">
         <v>0.911628</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.008279999999999999</v>
+        <v>0.008284</v>
       </c>
       <c r="C471" t="n">
         <v>0.9093020000000001</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.008505</v>
+        <v>0.008515</v>
       </c>
       <c r="C472" t="n">
         <v>0.906977</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.008964</v>
+        <v>0.008973999999999999</v>
       </c>
       <c r="C473" t="n">
         <v>0.904651</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.009357000000000001</v>
+        <v>0.009369000000000001</v>
       </c>
       <c r="C474" t="n">
         <v>0.902326</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.009382</v>
+        <v>0.009375</v>
       </c>
       <c r="C475" t="n">
         <v>0.9</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.009527000000000001</v>
+        <v>0.009528</v>
       </c>
       <c r="C476" t="n">
         <v>0.897674</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.009651</v>
+        <v>0.009662</v>
       </c>
       <c r="C477" t="n">
         <v>0.895349</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.009955</v>
+        <v>0.009911</v>
       </c>
       <c r="C478" t="n">
         <v>0.893023</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.010016</v>
+        <v>0.010031</v>
       </c>
       <c r="C479" t="n">
         <v>0.890698</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.010045</v>
+        <v>0.010061</v>
       </c>
       <c r="C480" t="n">
         <v>0.8883720000000001</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.010105</v>
+        <v>0.010097</v>
       </c>
       <c r="C481" t="n">
         <v>0.886047</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.010128</v>
+        <v>0.010103</v>
       </c>
       <c r="C482" t="n">
         <v>0.883721</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.010524</v>
+        <v>0.010534</v>
       </c>
       <c r="C483" t="n">
         <v>0.881395</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.010789</v>
+        <v>0.010804</v>
       </c>
       <c r="C484" t="n">
         <v>0.87907</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.010979</v>
+        <v>0.010983</v>
       </c>
       <c r="C485" t="n">
         <v>0.876744</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.011003</v>
+        <v>0.011033</v>
       </c>
       <c r="C486" t="n">
         <v>0.8744189999999999</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.011094</v>
+        <v>0.011103</v>
       </c>
       <c r="C487" t="n">
         <v>0.872093</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.011241</v>
+        <v>0.011253</v>
       </c>
       <c r="C488" t="n">
         <v>0.869767</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.011375</v>
+        <v>0.011391</v>
       </c>
       <c r="C489" t="n">
         <v>0.867442</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.011773</v>
+        <v>0.011795</v>
       </c>
       <c r="C490" t="n">
         <v>0.865116</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.011857</v>
+        <v>0.011872</v>
       </c>
       <c r="C491" t="n">
         <v>0.862791</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.012058</v>
+        <v>0.012034</v>
       </c>
       <c r="C492" t="n">
         <v>0.860465</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.012197</v>
+        <v>0.012198</v>
       </c>
       <c r="C493" t="n">
         <v>0.85814</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.012403</v>
+        <v>0.012401</v>
       </c>
       <c r="C494" t="n">
         <v>0.855814</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.012845</v>
+        <v>0.012858</v>
       </c>
       <c r="C495" t="n">
         <v>0.853488</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.012929</v>
+        <v>0.012927</v>
       </c>
       <c r="C496" t="n">
         <v>0.851163</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.013059</v>
+        <v>0.013053</v>
       </c>
       <c r="C497" t="n">
         <v>0.848837</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.013114</v>
+        <v>0.013124</v>
       </c>
       <c r="C498" t="n">
         <v>0.846512</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.013212</v>
+        <v>0.013169</v>
       </c>
       <c r="C499" t="n">
         <v>0.844186</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.013429</v>
+        <v>0.013459</v>
       </c>
       <c r="C500" t="n">
         <v>0.8418600000000001</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.013766</v>
+        <v>0.013776</v>
       </c>
       <c r="C501" t="n">
         <v>0.839535</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.013807</v>
+        <v>0.013834</v>
       </c>
       <c r="C502" t="n">
         <v>0.837209</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.014288</v>
+        <v>0.01427</v>
       </c>
       <c r="C503" t="n">
         <v>0.834884</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.014866</v>
+        <v>0.014861</v>
       </c>
       <c r="C504" t="n">
         <v>0.832558</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.014894</v>
+        <v>0.01492</v>
       </c>
       <c r="C505" t="n">
         <v>0.830233</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.015286</v>
+        <v>0.015298</v>
       </c>
       <c r="C506" t="n">
         <v>0.8279069999999999</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.015436</v>
+        <v>0.015433</v>
       </c>
       <c r="C507" t="n">
         <v>0.825581</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.015549</v>
+        <v>0.015566</v>
       </c>
       <c r="C508" t="n">
         <v>0.823256</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.01555</v>
+        <v>0.015574</v>
       </c>
       <c r="C509" t="n">
         <v>0.82093</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.015709</v>
+        <v>0.015721</v>
       </c>
       <c r="C510" t="n">
         <v>0.818605</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.015802</v>
+        <v>0.015827</v>
       </c>
       <c r="C511" t="n">
         <v>0.816279</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.015836</v>
+        <v>0.015835</v>
       </c>
       <c r="C512" t="n">
         <v>0.813953</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.016002</v>
+        <v>0.016029</v>
       </c>
       <c r="C513" t="n">
         <v>0.811628</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.016075</v>
+        <v>0.016091</v>
       </c>
       <c r="C514" t="n">
         <v>0.809302</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.016097</v>
+        <v>0.016103</v>
       </c>
       <c r="C515" t="n">
         <v>0.8069770000000001</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.016269</v>
+        <v>0.016283</v>
       </c>
       <c r="C516" t="n">
         <v>0.804651</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.017281</v>
+        <v>0.017297</v>
       </c>
       <c r="C518" t="n">
         <v>0.8</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.017454</v>
+        <v>0.017484</v>
       </c>
       <c r="C519" t="n">
         <v>0.797674</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.017643</v>
+        <v>0.017642</v>
       </c>
       <c r="C520" t="n">
         <v>0.795349</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.017878</v>
+        <v>0.017916</v>
       </c>
       <c r="C521" t="n">
         <v>0.793023</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.018526</v>
+        <v>0.018525</v>
       </c>
       <c r="C522" t="n">
         <v>0.790698</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.018685</v>
+        <v>0.018672</v>
       </c>
       <c r="C523" t="n">
         <v>0.788372</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.018725</v>
+        <v>0.018756</v>
       </c>
       <c r="C524" t="n">
         <v>0.7860470000000001</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.018856</v>
+        <v>0.018862</v>
       </c>
       <c r="C525" t="n">
         <v>0.783721</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.018881</v>
+        <v>0.018917</v>
       </c>
       <c r="C526" t="n">
         <v>0.781395</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.019133</v>
+        <v>0.01915</v>
       </c>
       <c r="C527" t="n">
         <v>0.77907</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.019438</v>
+        <v>0.019444</v>
       </c>
       <c r="C528" t="n">
         <v>0.776744</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.019806</v>
+        <v>0.019802</v>
       </c>
       <c r="C530" t="n">
         <v>0.772093</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.019892</v>
+        <v>0.019883</v>
       </c>
       <c r="C531" t="n">
         <v>0.769767</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.019927</v>
+        <v>0.019933</v>
       </c>
       <c r="C532" t="n">
         <v>0.767442</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.02028</v>
+        <v>0.020305</v>
       </c>
       <c r="C533" t="n">
         <v>0.765116</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.020738</v>
+        <v>0.020762</v>
       </c>
       <c r="C534" t="n">
         <v>0.762791</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.020887</v>
+        <v>0.02089</v>
       </c>
       <c r="C535" t="n">
         <v>0.7604649999999999</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.021384</v>
+        <v>0.021235</v>
       </c>
       <c r="C536" t="n">
         <v>0.75814</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.02174</v>
+        <v>0.02169</v>
       </c>
       <c r="C537" t="n">
         <v>0.755814</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.021865</v>
+        <v>0.021859</v>
       </c>
       <c r="C538" t="n">
         <v>0.753488</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.022018</v>
+        <v>0.022032</v>
       </c>
       <c r="C539" t="n">
         <v>0.751163</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.022751</v>
+        <v>0.022786</v>
       </c>
       <c r="C540" t="n">
         <v>0.748837</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.022835</v>
+        <v>0.022874</v>
       </c>
       <c r="C541" t="n">
         <v>0.746512</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.023087</v>
+        <v>0.02312</v>
       </c>
       <c r="C542" t="n">
         <v>0.744186</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.024357</v>
+        <v>0.024383</v>
       </c>
       <c r="C543" t="n">
         <v>0.74186</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.02447</v>
+        <v>0.02451</v>
       </c>
       <c r="C544" t="n">
         <v>0.7395350000000001</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.0247</v>
+        <v>0.024714</v>
       </c>
       <c r="C545" t="n">
         <v>0.737209</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.024718</v>
+        <v>0.024737</v>
       </c>
       <c r="C546" t="n">
         <v>0.734884</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.025093</v>
+        <v>0.025139</v>
       </c>
       <c r="C547" t="n">
         <v>0.732558</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.025205</v>
+        <v>0.025232</v>
       </c>
       <c r="C548" t="n">
         <v>0.730233</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.025624</v>
+        <v>0.025639</v>
       </c>
       <c r="C549" t="n">
         <v>0.727907</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.025638</v>
+        <v>0.025646</v>
       </c>
       <c r="C550" t="n">
         <v>0.725581</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.026096</v>
+        <v>0.026092</v>
       </c>
       <c r="C551" t="n">
         <v>0.723256</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.026106</v>
+        <v>0.026135</v>
       </c>
       <c r="C552" t="n">
         <v>0.72093</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.026309</v>
+        <v>0.026354</v>
       </c>
       <c r="C553" t="n">
         <v>0.718605</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.026397</v>
+        <v>0.026414</v>
       </c>
       <c r="C554" t="n">
         <v>0.716279</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.026675</v>
+        <v>0.02672</v>
       </c>
       <c r="C555" t="n">
         <v>0.7139529999999999</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.027298</v>
+        <v>0.027313</v>
       </c>
       <c r="C556" t="n">
         <v>0.711628</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.027654</v>
+        <v>0.027576</v>
       </c>
       <c r="C557" t="n">
         <v>0.709302</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.027773</v>
+        <v>0.027795</v>
       </c>
       <c r="C558" t="n">
         <v>0.706977</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.028097</v>
+        <v>0.028145</v>
       </c>
       <c r="C559" t="n">
         <v>0.704651</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.028171</v>
+        <v>0.028178</v>
       </c>
       <c r="C560" t="n">
         <v>0.702326</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.028223</v>
+        <v>0.028209</v>
       </c>
       <c r="C561" t="n">
         <v>0.7</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.028226</v>
+        <v>0.028258</v>
       </c>
       <c r="C562" t="n">
         <v>0.697674</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.028255</v>
+        <v>0.028306</v>
       </c>
       <c r="C563" t="n">
         <v>0.695349</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.028339</v>
+        <v>0.028346</v>
       </c>
       <c r="C564" t="n">
         <v>0.6930229999999999</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.028723</v>
+        <v>0.028748</v>
       </c>
       <c r="C565" t="n">
         <v>0.690698</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.028793</v>
+        <v>0.028833</v>
       </c>
       <c r="C566" t="n">
         <v>0.688372</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.029315</v>
+        <v>0.029351</v>
       </c>
       <c r="C567" t="n">
         <v>0.686047</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.029596</v>
+        <v>0.029634</v>
       </c>
       <c r="C568" t="n">
         <v>0.683721</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.029879</v>
+        <v>0.029922</v>
       </c>
       <c r="C569" t="n">
         <v>0.681395</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.030113</v>
+        <v>0.030123</v>
       </c>
       <c r="C570" t="n">
         <v>0.67907</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.030226</v>
+        <v>0.030253</v>
       </c>
       <c r="C571" t="n">
         <v>0.676744</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.030255</v>
+        <v>0.030284</v>
       </c>
       <c r="C572" t="n">
         <v>0.674419</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.03094</v>
+        <v>0.030894</v>
       </c>
       <c r="C573" t="n">
         <v>0.6720930000000001</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.03108</v>
+        <v>0.031076</v>
       </c>
       <c r="C574" t="n">
         <v>0.669767</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.031383</v>
+        <v>0.031416</v>
       </c>
       <c r="C575" t="n">
         <v>0.667442</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.031458</v>
+        <v>0.031421</v>
       </c>
       <c r="C576" t="n">
         <v>0.665116</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.031604</v>
+        <v>0.031627</v>
       </c>
       <c r="C577" t="n">
         <v>0.662791</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.031812</v>
+        <v>0.031777</v>
       </c>
       <c r="C578" t="n">
         <v>0.660465</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.031878</v>
+        <v>0.03194</v>
       </c>
       <c r="C579" t="n">
         <v>0.6581399999999999</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.032079</v>
+        <v>0.03212</v>
       </c>
       <c r="C580" t="n">
         <v>0.655814</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.032241</v>
+        <v>0.032268</v>
       </c>
       <c r="C581" t="n">
         <v>0.653488</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.032628</v>
+        <v>0.03265</v>
       </c>
       <c r="C582" t="n">
         <v>0.651163</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.033162</v>
+        <v>0.03314</v>
       </c>
       <c r="C583" t="n">
         <v>0.648837</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.03324</v>
+        <v>0.033195</v>
       </c>
       <c r="C584" t="n">
         <v>0.646512</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.033461</v>
+        <v>0.033503</v>
       </c>
       <c r="C585" t="n">
         <v>0.644186</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.033709</v>
+        <v>0.033766</v>
       </c>
       <c r="C586" t="n">
         <v>0.64186</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.033767</v>
+        <v>0.033795</v>
       </c>
       <c r="C587" t="n">
         <v>0.639535</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.034093</v>
+        <v>0.034088</v>
       </c>
       <c r="C588" t="n">
         <v>0.637209</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.034564</v>
+        <v>0.034624</v>
       </c>
       <c r="C589" t="n">
         <v>0.634884</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.034941</v>
+        <v>0.034992</v>
       </c>
       <c r="C590" t="n">
         <v>0.632558</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.034953</v>
+        <v>0.035022</v>
       </c>
       <c r="C591" t="n">
         <v>0.630233</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.035248</v>
+        <v>0.035262</v>
       </c>
       <c r="C592" t="n">
         <v>0.627907</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.03567</v>
+        <v>0.035639</v>
       </c>
       <c r="C593" t="n">
         <v>0.6255810000000001</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.036001</v>
+        <v>0.035992</v>
       </c>
       <c r="C594" t="n">
         <v>0.623256</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.036228</v>
+        <v>0.036275</v>
       </c>
       <c r="C595" t="n">
         <v>0.62093</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.036421</v>
+        <v>0.036487</v>
       </c>
       <c r="C596" t="n">
         <v>0.618605</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.036526</v>
+        <v>0.036552</v>
       </c>
       <c r="C597" t="n">
         <v>0.616279</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.036616</v>
+        <v>0.03664</v>
       </c>
       <c r="C598" t="n">
         <v>0.613953</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.037088</v>
+        <v>0.037139</v>
       </c>
       <c r="C599" t="n">
         <v>0.6116279999999999</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.037348</v>
+        <v>0.03734</v>
       </c>
       <c r="C600" t="n">
         <v>0.609302</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.037387</v>
+        <v>0.037435</v>
       </c>
       <c r="C601" t="n">
         <v>0.606977</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.037422</v>
+        <v>0.037467</v>
       </c>
       <c r="C602" t="n">
         <v>0.604651</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.037717</v>
+        <v>0.037693</v>
       </c>
       <c r="C603" t="n">
         <v>0.602326</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.037807</v>
+        <v>0.037852</v>
       </c>
       <c r="C604" t="n">
         <v>0.6</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.03804</v>
+        <v>0.038081</v>
       </c>
       <c r="C605" t="n">
         <v>0.597674</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.03823</v>
+        <v>0.0382</v>
       </c>
       <c r="C606" t="n">
         <v>0.595349</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.038259</v>
+        <v>0.03829</v>
       </c>
       <c r="C607" t="n">
         <v>0.593023</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.038329</v>
+        <v>0.03835</v>
       </c>
       <c r="C608" t="n">
         <v>0.5906979999999999</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.038759</v>
+        <v>0.03868</v>
       </c>
       <c r="C609" t="n">
         <v>0.588372</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.039066</v>
+        <v>0.039121</v>
       </c>
       <c r="C610" t="n">
         <v>0.586047</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.039642</v>
+        <v>0.039658</v>
       </c>
       <c r="C611" t="n">
         <v>0.583721</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.039886</v>
+        <v>0.03978</v>
       </c>
       <c r="C612" t="n">
         <v>0.581395</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.039919</v>
+        <v>0.039924</v>
       </c>
       <c r="C613" t="n">
         <v>0.57907</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.040012</v>
+        <v>0.039969</v>
       </c>
       <c r="C614" t="n">
         <v>0.576744</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.040016</v>
+        <v>0.040031</v>
       </c>
       <c r="C615" t="n">
         <v>0.574419</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.040477</v>
+        <v>0.04051</v>
       </c>
       <c r="C616" t="n">
         <v>0.572093</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.040767</v>
+        <v>0.040811</v>
       </c>
       <c r="C617" t="n">
         <v>0.569767</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.040883</v>
+        <v>0.040841</v>
       </c>
       <c r="C618" t="n">
         <v>0.567442</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.041258</v>
+        <v>0.041197</v>
       </c>
       <c r="C619" t="n">
         <v>0.565116</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.041452</v>
+        <v>0.041442</v>
       </c>
       <c r="C620" t="n">
         <v>0.562791</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.041777</v>
+        <v>0.041807</v>
       </c>
       <c r="C621" t="n">
         <v>0.560465</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.041792</v>
+        <v>0.041856</v>
       </c>
       <c r="C622" t="n">
         <v>0.55814</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.042122</v>
+        <v>0.042196</v>
       </c>
       <c r="C623" t="n">
         <v>0.555814</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.042471</v>
+        <v>0.042563</v>
       </c>
       <c r="C624" t="n">
         <v>0.553488</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.04255</v>
+        <v>0.042567</v>
       </c>
       <c r="C625" t="n">
         <v>0.551163</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.042612</v>
+        <v>0.042731</v>
       </c>
       <c r="C626" t="n">
         <v>0.548837</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.042868</v>
+        <v>0.042943</v>
       </c>
       <c r="C627" t="n">
         <v>0.546512</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.043047</v>
+        <v>0.04304</v>
       </c>
       <c r="C628" t="n">
         <v>0.5441859999999999</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.043047</v>
+        <v>0.043055</v>
       </c>
       <c r="C629" t="n">
         <v>0.54186</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.043926</v>
+        <v>0.043972</v>
       </c>
       <c r="C630" t="n">
         <v>0.539535</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.044264</v>
+        <v>0.044319</v>
       </c>
       <c r="C631" t="n">
         <v>0.537209</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.044576</v>
+        <v>0.044583</v>
       </c>
       <c r="C632" t="n">
         <v>0.534884</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.045421</v>
+        <v>0.045402</v>
       </c>
       <c r="C633" t="n">
         <v>0.532558</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.045649</v>
+        <v>0.045583</v>
       </c>
       <c r="C634" t="n">
         <v>0.530233</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.045669</v>
+        <v>0.045713</v>
       </c>
       <c r="C635" t="n">
         <v>0.527907</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.045973</v>
+        <v>0.045916</v>
       </c>
       <c r="C636" t="n">
         <v>0.525581</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.046822</v>
+        <v>0.046838</v>
       </c>
       <c r="C637" t="n">
         <v>0.5232560000000001</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.047573</v>
+        <v>0.047552</v>
       </c>
       <c r="C638" t="n">
         <v>0.52093</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.047638</v>
+        <v>0.047682</v>
       </c>
       <c r="C639" t="n">
         <v>0.518605</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.047992</v>
+        <v>0.048023</v>
       </c>
       <c r="C640" t="n">
         <v>0.516279</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.048408</v>
+        <v>0.048487</v>
       </c>
       <c r="C641" t="n">
         <v>0.513953</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.048494</v>
+        <v>0.048555</v>
       </c>
       <c r="C642" t="n">
         <v>0.511628</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.049307</v>
+        <v>0.049309</v>
       </c>
       <c r="C643" t="n">
         <v>0.509302</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.049614</v>
+        <v>0.049691</v>
       </c>
       <c r="C644" t="n">
         <v>0.506977</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.050085</v>
+        <v>0.050069</v>
       </c>
       <c r="C645" t="n">
         <v>0.504651</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.050116</v>
+        <v>0.05011</v>
       </c>
       <c r="C646" t="n">
         <v>0.5023260000000001</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.050121</v>
+        <v>0.050201</v>
       </c>
       <c r="C647" t="n">
         <v>0.5</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.050471</v>
+        <v>0.050433</v>
       </c>
       <c r="C648" t="n">
         <v>0.497674</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.05068</v>
+        <v>0.050693</v>
       </c>
       <c r="C649" t="n">
         <v>0.495349</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.051971</v>
+        <v>0.052025</v>
       </c>
       <c r="C650" t="n">
         <v>0.493023</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.052036</v>
+        <v>0.052073</v>
       </c>
       <c r="C651" t="n">
         <v>0.490698</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.052892</v>
+        <v>0.05279</v>
       </c>
       <c r="C652" t="n">
         <v>0.488372</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.053114</v>
+        <v>0.053174</v>
       </c>
       <c r="C653" t="n">
         <v>0.486047</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.053134</v>
+        <v>0.053207</v>
       </c>
       <c r="C654" t="n">
         <v>0.483721</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.05341</v>
+        <v>0.053483</v>
       </c>
       <c r="C655" t="n">
         <v>0.481395</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.053509</v>
+        <v>0.053563</v>
       </c>
       <c r="C656" t="n">
         <v>0.47907</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.054621</v>
+        <v>0.054673</v>
       </c>
       <c r="C657" t="n">
         <v>0.476744</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.05465</v>
+        <v>0.054745</v>
       </c>
       <c r="C658" t="n">
         <v>0.474419</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.054955</v>
+        <v>0.055027</v>
       </c>
       <c r="C659" t="n">
         <v>0.472093</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.055341</v>
+        <v>0.055458</v>
       </c>
       <c r="C660" t="n">
         <v>0.469767</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.055476</v>
+        <v>0.055594</v>
       </c>
       <c r="C661" t="n">
         <v>0.467442</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.056461</v>
+        <v>0.056523</v>
       </c>
       <c r="C662" t="n">
         <v>0.465116</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.056667</v>
+        <v>0.056765</v>
       </c>
       <c r="C663" t="n">
         <v>0.462791</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.056884</v>
+        <v>0.05699</v>
       </c>
       <c r="C664" t="n">
         <v>0.460465</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.057703</v>
+        <v>0.057736</v>
       </c>
       <c r="C665" t="n">
         <v>0.45814</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.059305</v>
+        <v>0.059408</v>
       </c>
       <c r="C666" t="n">
         <v>0.455814</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.059569</v>
+        <v>0.059658</v>
       </c>
       <c r="C667" t="n">
         <v>0.453488</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.060159</v>
+        <v>0.060102</v>
       </c>
       <c r="C668" t="n">
         <v>0.451163</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.060251</v>
+        <v>0.060346</v>
       </c>
       <c r="C669" t="n">
         <v>0.448837</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.060688</v>
+        <v>0.060702</v>
       </c>
       <c r="C670" t="n">
         <v>0.446512</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.060947</v>
+        <v>0.061062</v>
       </c>
       <c r="C671" t="n">
         <v>0.444186</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.061281</v>
+        <v>0.061295</v>
       </c>
       <c r="C672" t="n">
         <v>0.44186</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.06138</v>
+        <v>0.061404</v>
       </c>
       <c r="C673" t="n">
         <v>0.439535</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.061679</v>
+        <v>0.061687</v>
       </c>
       <c r="C674" t="n">
         <v>0.437209</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.062088</v>
+        <v>0.062001</v>
       </c>
       <c r="C675" t="n">
         <v>0.434884</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.062809</v>
+        <v>0.062843</v>
       </c>
       <c r="C676" t="n">
         <v>0.432558</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.063051</v>
+        <v>0.063054</v>
       </c>
       <c r="C677" t="n">
         <v>0.430233</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.06358900000000001</v>
+        <v>0.06365899999999999</v>
       </c>
       <c r="C678" t="n">
         <v>0.427907</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.06368799999999999</v>
+        <v>0.06381000000000001</v>
       </c>
       <c r="C679" t="n">
         <v>0.425581</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.064133</v>
+        <v>0.064181</v>
       </c>
       <c r="C680" t="n">
         <v>0.423256</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.06421399999999999</v>
+        <v>0.06424100000000001</v>
       </c>
       <c r="C681" t="n">
         <v>0.42093</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.064572</v>
+        <v>0.064583</v>
       </c>
       <c r="C682" t="n">
         <v>0.418605</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.064583</v>
+        <v>0.06465899999999999</v>
       </c>
       <c r="C683" t="n">
         <v>0.416279</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.064606</v>
+        <v>0.06468699999999999</v>
       </c>
       <c r="C684" t="n">
         <v>0.413953</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.064692</v>
+        <v>0.06479500000000001</v>
       </c>
       <c r="C685" t="n">
         <v>0.411628</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.065197</v>
+        <v>0.065237</v>
       </c>
       <c r="C686" t="n">
         <v>0.409302</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.065798</v>
+        <v>0.065909</v>
       </c>
       <c r="C687" t="n">
         <v>0.406977</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.066097</v>
+        <v>0.065981</v>
       </c>
       <c r="C688" t="n">
         <v>0.404651</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.066898</v>
+        <v>0.066972</v>
       </c>
       <c r="C689" t="n">
         <v>0.402326</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.067097</v>
+        <v>0.067037</v>
       </c>
       <c r="C690" t="n">
         <v>0.4</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.06794500000000001</v>
+        <v>0.067979</v>
       </c>
       <c r="C691" t="n">
         <v>0.397674</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.068067</v>
+        <v>0.06811200000000001</v>
       </c>
       <c r="C692" t="n">
         <v>0.395349</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.068117</v>
+        <v>0.06822499999999999</v>
       </c>
       <c r="C693" t="n">
         <v>0.393023</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.06820900000000001</v>
+        <v>0.068272</v>
       </c>
       <c r="C694" t="n">
         <v>0.390698</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.068635</v>
+        <v>0.06851400000000001</v>
       </c>
       <c r="C695" t="n">
         <v>0.388372</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.069091</v>
+        <v>0.06922499999999999</v>
       </c>
       <c r="C696" t="n">
         <v>0.386047</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.06965</v>
+        <v>0.06972100000000001</v>
       </c>
       <c r="C697" t="n">
         <v>0.383721</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.069913</v>
+        <v>0.06995</v>
       </c>
       <c r="C698" t="n">
         <v>0.381395</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.07006800000000001</v>
+        <v>0.070117</v>
       </c>
       <c r="C699" t="n">
         <v>0.37907</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.07027600000000001</v>
+        <v>0.070287</v>
       </c>
       <c r="C700" t="n">
         <v>0.376744</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.070341</v>
+        <v>0.070423</v>
       </c>
       <c r="C701" t="n">
         <v>0.374419</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.07053</v>
+        <v>0.070567</v>
       </c>
       <c r="C702" t="n">
         <v>0.372093</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.071239</v>
+        <v>0.070983</v>
       </c>
       <c r="C703" t="n">
         <v>0.369767</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.071612</v>
+        <v>0.071742</v>
       </c>
       <c r="C704" t="n">
         <v>0.367442</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.071657</v>
+        <v>0.071773</v>
       </c>
       <c r="C705" t="n">
         <v>0.365116</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.07179099999999999</v>
+        <v>0.07191400000000001</v>
       </c>
       <c r="C706" t="n">
         <v>0.362791</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.07194200000000001</v>
+        <v>0.07204099999999999</v>
       </c>
       <c r="C707" t="n">
         <v>0.360465</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.072072</v>
+        <v>0.07206600000000001</v>
       </c>
       <c r="C708" t="n">
         <v>0.35814</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.07215000000000001</v>
+        <v>0.07215199999999999</v>
       </c>
       <c r="C709" t="n">
         <v>0.355814</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.072521</v>
+        <v>0.072562</v>
       </c>
       <c r="C710" t="n">
         <v>0.353488</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.073001</v>
+        <v>0.073126</v>
       </c>
       <c r="C711" t="n">
         <v>0.351163</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.07352599999999999</v>
+        <v>0.07355100000000001</v>
       </c>
       <c r="C712" t="n">
         <v>0.348837</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.073935</v>
+        <v>0.074075</v>
       </c>
       <c r="C713" t="n">
         <v>0.346512</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.074293</v>
+        <v>0.074295</v>
       </c>
       <c r="C714" t="n">
         <v>0.344186</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.074308</v>
+        <v>0.074366</v>
       </c>
       <c r="C715" t="n">
         <v>0.34186</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.07439</v>
+        <v>0.074518</v>
       </c>
       <c r="C716" t="n">
         <v>0.339535</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.075057</v>
+        <v>0.075074</v>
       </c>
       <c r="C717" t="n">
         <v>0.337209</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.07510699999999999</v>
+        <v>0.075159</v>
       </c>
       <c r="C718" t="n">
         <v>0.334884</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.075347</v>
+        <v>0.075418</v>
       </c>
       <c r="C719" t="n">
         <v>0.332558</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.075352</v>
+        <v>0.075437</v>
       </c>
       <c r="C720" t="n">
         <v>0.330233</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.07538</v>
+        <v>0.075487</v>
       </c>
       <c r="C721" t="n">
         <v>0.327907</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.07549699999999999</v>
+        <v>0.075603</v>
       </c>
       <c r="C722" t="n">
         <v>0.325581</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.077775</v>
+        <v>0.077767</v>
       </c>
       <c r="C723" t="n">
         <v>0.323256</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.07926</v>
+        <v>0.079346</v>
       </c>
       <c r="C724" t="n">
         <v>0.32093</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.079387</v>
+        <v>0.079559</v>
       </c>
       <c r="C725" t="n">
         <v>0.318605</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.079656</v>
+        <v>0.079747</v>
       </c>
       <c r="C726" t="n">
         <v>0.316279</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.07981100000000001</v>
+        <v>0.07978499999999999</v>
       </c>
       <c r="C727" t="n">
         <v>0.313953</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.080396</v>
+        <v>0.080494</v>
       </c>
       <c r="C728" t="n">
         <v>0.311628</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.080737</v>
+        <v>0.080925</v>
       </c>
       <c r="C729" t="n">
         <v>0.309302</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.08110100000000001</v>
+        <v>0.080987</v>
       </c>
       <c r="C730" t="n">
         <v>0.306977</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.082189</v>
+        <v>0.082218</v>
       </c>
       <c r="C731" t="n">
         <v>0.304651</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.082325</v>
+        <v>0.082342</v>
       </c>
       <c r="C732" t="n">
         <v>0.302326</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.083159</v>
+        <v>0.082728</v>
       </c>
       <c r="C733" t="n">
         <v>0.3</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.083179</v>
+        <v>0.08312799999999999</v>
       </c>
       <c r="C734" t="n">
         <v>0.297674</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.08422</v>
+        <v>0.08404200000000001</v>
       </c>
       <c r="C735" t="n">
         <v>0.295349</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.084332</v>
+        <v>0.084325</v>
       </c>
       <c r="C736" t="n">
         <v>0.293023</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.084463</v>
+        <v>0.084468</v>
       </c>
       <c r="C737" t="n">
         <v>0.290698</v>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.085137</v>
+        <v>0.085188</v>
       </c>
       <c r="C738" t="n">
         <v>0.288372</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.085201</v>
+        <v>0.085354</v>
       </c>
       <c r="C739" t="n">
         <v>0.286047</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.085684</v>
+        <v>0.085615</v>
       </c>
       <c r="C740" t="n">
         <v>0.283721</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.085842</v>
+        <v>0.085952</v>
       </c>
       <c r="C741" t="n">
         <v>0.281395</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.086657</v>
+        <v>0.086726</v>
       </c>
       <c r="C742" t="n">
         <v>0.27907</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.086856</v>
+        <v>0.086868</v>
       </c>
       <c r="C743" t="n">
         <v>0.276744</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.087024</v>
+        <v>0.087022</v>
       </c>
       <c r="C744" t="n">
         <v>0.274419</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.087626</v>
+        <v>0.08759500000000001</v>
       </c>
       <c r="C745" t="n">
         <v>0.272093</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.08798599999999999</v>
+        <v>0.087839</v>
       </c>
       <c r="C746" t="n">
         <v>0.269767</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.088687</v>
+        <v>0.088897</v>
       </c>
       <c r="C747" t="n">
         <v>0.267442</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.089295</v>
+        <v>0.089339</v>
       </c>
       <c r="C748" t="n">
         <v>0.265116</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.089339</v>
+        <v>0.08946999999999999</v>
       </c>
       <c r="C749" t="n">
         <v>0.262791</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.089613</v>
+        <v>0.08951199999999999</v>
       </c>
       <c r="C750" t="n">
         <v>0.260465</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.090735</v>
+        <v>0.09064999999999999</v>
       </c>
       <c r="C751" t="n">
         <v>0.25814</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.09078799999999999</v>
+        <v>0.090794</v>
       </c>
       <c r="C752" t="n">
         <v>0.255814</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.091819</v>
+        <v>0.09194099999999999</v>
       </c>
       <c r="C753" t="n">
         <v>0.253488</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.092167</v>
+        <v>0.092073</v>
       </c>
       <c r="C754" t="n">
         <v>0.251163</v>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.092707</v>
+        <v>0.09280099999999999</v>
       </c>
       <c r="C755" t="n">
         <v>0.248837</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.093142</v>
+        <v>0.093204</v>
       </c>
       <c r="C756" t="n">
         <v>0.246512</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.09317300000000001</v>
+        <v>0.093371</v>
       </c>
       <c r="C757" t="n">
         <v>0.244186</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.094234</v>
+        <v>0.09440999999999999</v>
       </c>
       <c r="C758" t="n">
         <v>0.24186</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.094719</v>
+        <v>0.094754</v>
       </c>
       <c r="C759" t="n">
         <v>0.239535</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.095026</v>
+        <v>0.09515899999999999</v>
       </c>
       <c r="C760" t="n">
         <v>0.237209</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.09615600000000001</v>
+        <v>0.096305</v>
       </c>
       <c r="C761" t="n">
         <v>0.234884</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.097334</v>
+        <v>0.09754500000000001</v>
       </c>
       <c r="C762" t="n">
         <v>0.232558</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.09777</v>
+        <v>0.09787700000000001</v>
       </c>
       <c r="C763" t="n">
         <v>0.230233</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.09872599999999999</v>
+        <v>0.098678</v>
       </c>
       <c r="C764" t="n">
         <v>0.227907</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.099217</v>
+        <v>0.09934900000000001</v>
       </c>
       <c r="C765" t="n">
         <v>0.225581</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.099383</v>
+        <v>0.09955600000000001</v>
       </c>
       <c r="C766" t="n">
         <v>0.223256</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.099428</v>
+        <v>0.099643</v>
       </c>
       <c r="C767" t="n">
         <v>0.22093</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.10077</v>
+        <v>0.100897</v>
       </c>
       <c r="C768" t="n">
         <v>0.218605</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.101665</v>
+        <v>0.101748</v>
       </c>
       <c r="C769" t="n">
         <v>0.216279</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.101851</v>
+        <v>0.102031</v>
       </c>
       <c r="C770" t="n">
         <v>0.213953</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.102147</v>
+        <v>0.102242</v>
       </c>
       <c r="C771" t="n">
         <v>0.211628</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.105948</v>
+        <v>0.106032</v>
       </c>
       <c r="C772" t="n">
         <v>0.209302</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.106661</v>
+        <v>0.106771</v>
       </c>
       <c r="C773" t="n">
         <v>0.206977</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.107941</v>
+        <v>0.108079</v>
       </c>
       <c r="C774" t="n">
         <v>0.204651</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.108305</v>
+        <v>0.108507</v>
       </c>
       <c r="C775" t="n">
         <v>0.202326</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.112361</v>
+        <v>0.112556</v>
       </c>
       <c r="C776" t="n">
         <v>0.2</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.112851</v>
+        <v>0.112903</v>
       </c>
       <c r="C777" t="n">
         <v>0.197674</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.113494</v>
+        <v>0.11353</v>
       </c>
       <c r="C778" t="n">
         <v>0.195349</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.115626</v>
+        <v>0.115827</v>
       </c>
       <c r="C779" t="n">
         <v>0.193023</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.116928</v>
+        <v>0.117003</v>
       </c>
       <c r="C780" t="n">
         <v>0.190698</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.117034</v>
+        <v>0.117069</v>
       </c>
       <c r="C781" t="n">
         <v>0.188372</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.119355</v>
+        <v>0.119343</v>
       </c>
       <c r="C782" t="n">
         <v>0.186047</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.119389</v>
+        <v>0.11955</v>
       </c>
       <c r="C783" t="n">
         <v>0.183721</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.120886</v>
+        <v>0.120975</v>
       </c>
       <c r="C784" t="n">
         <v>0.181395</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.122062</v>
+        <v>0.122184</v>
       </c>
       <c r="C785" t="n">
         <v>0.17907</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.124185</v>
+        <v>0.124232</v>
       </c>
       <c r="C786" t="n">
         <v>0.176744</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.124229</v>
+        <v>0.124245</v>
       </c>
       <c r="C787" t="n">
         <v>0.174419</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.12434</v>
+        <v>0.124458</v>
       </c>
       <c r="C788" t="n">
         <v>0.172093</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.125393</v>
+        <v>0.125234</v>
       </c>
       <c r="C789" t="n">
         <v>0.169767</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>0.12597</v>
+        <v>0.126103</v>
       </c>
       <c r="C790" t="n">
         <v>0.167442</v>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>0.126858</v>
+        <v>0.126929</v>
       </c>
       <c r="C791" t="n">
         <v>0.165116</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>0.127056</v>
+        <v>0.126979</v>
       </c>
       <c r="C792" t="n">
         <v>0.162791</v>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>0.127871</v>
+        <v>0.127728</v>
       </c>
       <c r="C793" t="n">
         <v>0.160465</v>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>0.128353</v>
+        <v>0.128481</v>
       </c>
       <c r="C794" t="n">
         <v>0.15814</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.128693</v>
+        <v>0.128875</v>
       </c>
       <c r="C795" t="n">
         <v>0.155814</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.129268</v>
+        <v>0.12934</v>
       </c>
       <c r="C796" t="n">
         <v>0.153488</v>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>0.130568</v>
+        <v>0.130382</v>
       </c>
       <c r="C797" t="n">
         <v>0.151163</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>0.133341</v>
+        <v>0.133384</v>
       </c>
       <c r="C798" t="n">
         <v>0.148837</v>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>0.133416</v>
+        <v>0.133507</v>
       </c>
       <c r="C799" t="n">
         <v>0.146512</v>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>0.134803</v>
+        <v>0.134924</v>
       </c>
       <c r="C800" t="n">
         <v>0.144186</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="B801" t="n">
-        <v>0.134823</v>
+        <v>0.134929</v>
       </c>
       <c r="C801" t="n">
         <v>0.14186</v>
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="B802" t="n">
-        <v>0.134889</v>
+        <v>0.135091</v>
       </c>
       <c r="C802" t="n">
         <v>0.139535</v>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="B803" t="n">
-        <v>0.135322</v>
+        <v>0.135527</v>
       </c>
       <c r="C803" t="n">
         <v>0.137209</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>0.136479</v>
+        <v>0.136775</v>
       </c>
       <c r="C804" t="n">
         <v>0.134884</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="B805" t="n">
-        <v>0.138144</v>
+        <v>0.138536</v>
       </c>
       <c r="C805" t="n">
         <v>0.132558</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="B806" t="n">
-        <v>0.138785</v>
+        <v>0.138828</v>
       </c>
       <c r="C806" t="n">
         <v>0.130233</v>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="B807" t="n">
-        <v>0.142216</v>
+        <v>0.142469</v>
       </c>
       <c r="C807" t="n">
         <v>0.127907</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>0.145372</v>
+        <v>0.145245</v>
       </c>
       <c r="C808" t="n">
         <v>0.125581</v>
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>0.146421</v>
+        <v>0.146683</v>
       </c>
       <c r="C809" t="n">
         <v>0.123256</v>
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>0.147224</v>
+        <v>0.147097</v>
       </c>
       <c r="C810" t="n">
         <v>0.12093</v>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0.153113</v>
+        <v>0.153228</v>
       </c>
       <c r="C811" t="n">
         <v>0.118605</v>
@@ -10970,7 +10970,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>0.154657</v>
+        <v>0.154805</v>
       </c>
       <c r="C812" t="n">
         <v>0.116279</v>
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.155726</v>
+        <v>0.155551</v>
       </c>
       <c r="C813" t="n">
         <v>0.113953</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>0.156101</v>
+        <v>0.155733</v>
       </c>
       <c r="C814" t="n">
         <v>0.111628</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>0.158058</v>
+        <v>0.158168</v>
       </c>
       <c r="C815" t="n">
         <v>0.109302</v>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>0.159915</v>
+        <v>0.159895</v>
       </c>
       <c r="C816" t="n">
         <v>0.106977</v>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>0.163767</v>
+        <v>0.163976</v>
       </c>
       <c r="C817" t="n">
         <v>0.104651</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>0.163984</v>
+        <v>0.164151</v>
       </c>
       <c r="C818" t="n">
         <v>0.102326</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="B819" t="n">
-        <v>0.166755</v>
+        <v>0.166474</v>
       </c>
       <c r="C819" t="n">
         <v>0.1</v>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="B820" t="n">
-        <v>0.168603</v>
+        <v>0.168632</v>
       </c>
       <c r="C820" t="n">
         <v>0.097674</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>0.170408</v>
+        <v>0.170824</v>
       </c>
       <c r="C821" t="n">
         <v>0.095349</v>
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="B822" t="n">
-        <v>0.170813</v>
+        <v>0.170871</v>
       </c>
       <c r="C822" t="n">
         <v>0.09302299999999999</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>0.173669</v>
+        <v>0.173332</v>
       </c>
       <c r="C823" t="n">
         <v>0.090698</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>0.173669</v>
+        <v>0.173332</v>
       </c>
       <c r="C824" t="n">
         <v>0.08837200000000001</v>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>0.173669</v>
+        <v>0.173332</v>
       </c>
       <c r="C825" t="n">
         <v>0.086047</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.173949</v>
+        <v>0.174256</v>
       </c>
       <c r="C826" t="n">
         <v>0.083721</v>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>0.180248</v>
+        <v>0.180291</v>
       </c>
       <c r="C827" t="n">
         <v>0.081395</v>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="B828" t="n">
-        <v>0.183297</v>
+        <v>0.183205</v>
       </c>
       <c r="C828" t="n">
         <v>0.07907</v>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>0.184944</v>
+        <v>0.184954</v>
       </c>
       <c r="C829" t="n">
         <v>0.07674400000000001</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>0.185032</v>
+        <v>0.185242</v>
       </c>
       <c r="C830" t="n">
         <v>0.074419</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>0.190994</v>
+        <v>0.1911</v>
       </c>
       <c r="C831" t="n">
         <v>0.072093</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B832" t="n">
-        <v>0.195022</v>
+        <v>0.195277</v>
       </c>
       <c r="C832" t="n">
         <v>0.069767</v>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>0.196468</v>
+        <v>0.196811</v>
       </c>
       <c r="C833" t="n">
         <v>0.067442</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>0.198213</v>
+        <v>0.198557</v>
       </c>
       <c r="C834" t="n">
         <v>0.06511599999999999</v>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="B835" t="n">
-        <v>0.212103</v>
+        <v>0.212371</v>
       </c>
       <c r="C835" t="n">
         <v>0.062791</v>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>0.212711</v>
+        <v>0.213001</v>
       </c>
       <c r="C836" t="n">
         <v>0.060465</v>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>0.2207</v>
+        <v>0.220753</v>
       </c>
       <c r="C837" t="n">
         <v>0.05814</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>0.222038</v>
+        <v>0.222097</v>
       </c>
       <c r="C838" t="n">
         <v>0.055814</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.222369</v>
+        <v>0.222764</v>
       </c>
       <c r="C839" t="n">
         <v>0.053488</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>0.224057</v>
+        <v>0.223806</v>
       </c>
       <c r="C840" t="n">
         <v>0.051163</v>
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.224132</v>
+        <v>0.224246</v>
       </c>
       <c r="C841" t="n">
         <v>0.048837</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.22845</v>
+        <v>0.22779</v>
       </c>
       <c r="C842" t="n">
         <v>0.046512</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="B843" t="n">
-        <v>0.25557</v>
+        <v>0.256024</v>
       </c>
       <c r="C843" t="n">
         <v>0.044186</v>
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>0.264792</v>
+        <v>0.26513</v>
       </c>
       <c r="C844" t="n">
         <v>0.04186</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.273416</v>
+        <v>0.273655</v>
       </c>
       <c r="C845" t="n">
         <v>0.039535</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>0.280968</v>
+        <v>0.280619</v>
       </c>
       <c r="C846" t="n">
         <v>0.037209</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>0.310594</v>
+        <v>0.310768</v>
       </c>
       <c r="C847" t="n">
         <v>0.034884</v>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>0.311532</v>
+        <v>0.31212</v>
       </c>
       <c r="C848" t="n">
         <v>0.032558</v>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>0.313572</v>
+        <v>0.313599</v>
       </c>
       <c r="C849" t="n">
         <v>0.030233</v>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>0.347652</v>
+        <v>0.347408</v>
       </c>
       <c r="C850" t="n">
         <v>0.027907</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>0.358997</v>
+        <v>0.359666</v>
       </c>
       <c r="C851" t="n">
         <v>0.025581</v>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.363725</v>
+        <v>0.364409</v>
       </c>
       <c r="C852" t="n">
         <v>0.023256</v>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>0.378047</v>
+        <v>0.377683</v>
       </c>
       <c r="C853" t="n">
         <v>0.02093</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.388232</v>
+        <v>0.388225</v>
       </c>
       <c r="C854" t="n">
         <v>0.018605</v>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>0.39996</v>
+        <v>0.400477</v>
       </c>
       <c r="C855" t="n">
         <v>0.016279</v>
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>0.540816</v>
+        <v>0.540237</v>
       </c>
       <c r="C856" t="n">
         <v>0.013953</v>
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>0.551154</v>
+        <v>0.551625</v>
       </c>
       <c r="C857" t="n">
         <v>0.011628</v>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>0.682852</v>
+        <v>0.684051</v>
       </c>
       <c r="C858" t="n">
         <v>0.009302</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.70228</v>
+        <v>0.703035</v>
       </c>
       <c r="C859" t="n">
         <v>0.006977</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>1.047587</v>
+        <v>1.049405</v>
       </c>
       <c r="C860" t="n">
         <v>0.004651</v>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="B861" t="n">
-        <v>1.344885</v>
+        <v>1.348523</v>
       </c>
       <c r="C861" t="n">
         <v>0.002326</v>
